--- a/data/enobnu/calendario.xlsx
+++ b/data/enobnu/calendario.xlsx
@@ -503,10 +503,10 @@
     <col width="13" customWidth="1" min="4" max="4"/>
     <col width="11" customWidth="1" min="5" max="5"/>
     <col width="22" customWidth="1" min="6" max="6"/>
-    <col width="28" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="40" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="45" customWidth="1" min="10" max="10"/>
+    <col width="35" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -750,7 +750,7 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>Lógica 3</t>
+          <t>Lógica 3 teórico-práctico</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr"/>
@@ -790,7 +790,7 @@
       </c>
       <c r="G7" s="5" t="inlineStr">
         <is>
-          <t>Lógica 3</t>
+          <t>Sin Seminario</t>
         </is>
       </c>
       <c r="H7" s="5" t="inlineStr"/>
@@ -834,7 +834,7 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>Repaso (semana mechona)</t>
+          <t>Modelos y Derivadas 1 teórico-práctico</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr"/>
@@ -874,7 +874,7 @@
       </c>
       <c r="G9" s="5" t="inlineStr">
         <is>
-          <t>Repaso (semana mechona)</t>
+          <t>Sin Seminario (semana mechona)</t>
         </is>
       </c>
       <c r="H9" s="5" t="inlineStr"/>
@@ -914,7 +914,7 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>Modelos y Derivadas 1</t>
+          <t>Modelos y Derivadas 2</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr"/>
@@ -954,24 +954,16 @@
       </c>
       <c r="G11" s="5" t="inlineStr">
         <is>
-          <t>Modelos y Derivadas 1</t>
-        </is>
-      </c>
-      <c r="H11" s="8" t="inlineStr">
-        <is>
-          <t>Certamen</t>
-        </is>
-      </c>
+          <t>Modelos y Derivadas 2</t>
+        </is>
+      </c>
+      <c r="H11" s="5" t="inlineStr"/>
       <c r="I11" s="5" t="inlineStr">
         <is>
           <t>JCS</t>
         </is>
       </c>
-      <c r="J11" s="5" t="inlineStr">
-        <is>
-          <t>Certamen 1</t>
-        </is>
-      </c>
+      <c r="J11" s="5" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
@@ -1002,7 +994,7 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>Modelos y Derivadas 2</t>
+          <t>Modelos y Derivadas 3</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr"/>
@@ -1042,7 +1034,7 @@
       </c>
       <c r="G13" s="5" t="inlineStr">
         <is>
-          <t>Modelos y Derivadas 2</t>
+          <t>Modelos y Derivadas 3</t>
         </is>
       </c>
       <c r="H13" s="5" t="inlineStr"/>
@@ -1122,7 +1114,7 @@
       </c>
       <c r="G15" s="5" t="inlineStr">
         <is>
-          <t>Certamen 1</t>
+          <t>Sin Seminario</t>
         </is>
       </c>
       <c r="H15" s="5" t="inlineStr"/>
@@ -1162,7 +1154,7 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>Modelos y Derivadas 3</t>
+          <t>Modelos y Derivadas 4</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr"/>
@@ -1202,7 +1194,7 @@
       </c>
       <c r="G17" s="5" t="inlineStr">
         <is>
-          <t>Modelos y Derivadas 3</t>
+          <t>Revision Certamen</t>
         </is>
       </c>
       <c r="H17" s="5" t="inlineStr"/>
@@ -1242,7 +1234,7 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>Modelos y Derivadas 4</t>
+          <t>Actividad Autónoma Portafolio</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr"/>
@@ -1525,21 +1517,13 @@
           <t>Linealización de modelos</t>
         </is>
       </c>
-      <c r="H25" s="8" t="inlineStr">
-        <is>
-          <t>Trabajo práctico</t>
-        </is>
-      </c>
+      <c r="H25" s="5" t="inlineStr"/>
       <c r="I25" s="5" t="inlineStr">
         <is>
           <t>JCS</t>
         </is>
       </c>
-      <c r="J25" s="5" t="inlineStr">
-        <is>
-          <t>Trabajo Práctico</t>
-        </is>
-      </c>
+      <c r="J25" s="5" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
@@ -1733,13 +1717,21 @@
           <t>Trigonometría y Vectores 3</t>
         </is>
       </c>
-      <c r="H30" s="2" t="inlineStr"/>
+      <c r="H30" s="8" t="inlineStr">
+        <is>
+          <t>Control</t>
+        </is>
+      </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
           <t>AR</t>
         </is>
       </c>
-      <c r="J30" s="2" t="inlineStr"/>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>Taller Unidad 1</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="n">
@@ -1773,21 +1765,13 @@
           <t>Trigonometría y Vectores 3</t>
         </is>
       </c>
-      <c r="H31" s="8" t="inlineStr">
-        <is>
-          <t>Control</t>
-        </is>
-      </c>
+      <c r="H31" s="5" t="inlineStr"/>
       <c r="I31" s="5" t="inlineStr">
         <is>
           <t>JCS</t>
         </is>
       </c>
-      <c r="J31" s="5" t="inlineStr">
-        <is>
-          <t>Taller Unidad 1 | Taller Unidad 2 | Taller Unidad 3</t>
-        </is>
-      </c>
+      <c r="J31" s="5" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
@@ -1861,21 +1845,13 @@
           <t>Certamen 2</t>
         </is>
       </c>
-      <c r="H33" s="8" t="inlineStr">
-        <is>
-          <t>Certamen</t>
-        </is>
-      </c>
+      <c r="H33" s="5" t="inlineStr"/>
       <c r="I33" s="5" t="inlineStr">
         <is>
           <t>JCS</t>
         </is>
       </c>
-      <c r="J33" s="5" t="inlineStr">
-        <is>
-          <t>Certamen 2</t>
-        </is>
-      </c>
+      <c r="J33" s="5" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="9" t="n">
@@ -2037,21 +2013,13 @@
           <t>Examen Primera Oportunidad</t>
         </is>
       </c>
-      <c r="H37" s="8" t="inlineStr">
-        <is>
-          <t>Examen</t>
-        </is>
-      </c>
+      <c r="H37" s="5" t="inlineStr"/>
       <c r="I37" s="5" t="inlineStr">
         <is>
           <t>JCS</t>
         </is>
       </c>
-      <c r="J37" s="5" t="inlineStr">
-        <is>
-          <t>Examen 1</t>
-        </is>
-      </c>
+      <c r="J37" s="5" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
@@ -2125,21 +2093,13 @@
           <t>Examen Segunda Oportunidad</t>
         </is>
       </c>
-      <c r="H39" s="8" t="inlineStr">
-        <is>
-          <t>Examen</t>
-        </is>
-      </c>
+      <c r="H39" s="5" t="inlineStr"/>
       <c r="I39" s="5" t="inlineStr">
         <is>
           <t>JCS</t>
         </is>
       </c>
-      <c r="J39" s="5" t="inlineStr">
-        <is>
-          <t>Examen 2</t>
-        </is>
-      </c>
+      <c r="J39" s="5" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
@@ -2330,7 +2290,7 @@
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>Lógica 3</t>
+          <t>Lógica 3 teórico-práctico</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr"/>
@@ -2370,7 +2330,7 @@
       </c>
       <c r="G45" s="12" t="inlineStr">
         <is>
-          <t>Lógica 3</t>
+          <t>Sin Seminario</t>
         </is>
       </c>
       <c r="H45" s="12" t="inlineStr"/>
@@ -2414,7 +2374,7 @@
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>Repaso (semana mechona)</t>
+          <t>Sin Clase (semana mechona)</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr"/>
@@ -2454,7 +2414,7 @@
       </c>
       <c r="G47" s="5" t="inlineStr">
         <is>
-          <t>Repaso (semana mechona)</t>
+          <t>Modelos y Derivadas 1 teórico-práctico</t>
         </is>
       </c>
       <c r="H47" s="5" t="inlineStr"/>
@@ -2494,7 +2454,7 @@
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>Modelos y Derivadas 1</t>
+          <t>Modelos y Derivadas 2</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr"/>
@@ -2534,24 +2494,16 @@
       </c>
       <c r="G49" s="5" t="inlineStr">
         <is>
-          <t>Modelos y Derivadas 1</t>
-        </is>
-      </c>
-      <c r="H49" s="8" t="inlineStr">
-        <is>
-          <t>Certamen</t>
-        </is>
-      </c>
+          <t>Modelos y Derivadas 2</t>
+        </is>
+      </c>
+      <c r="H49" s="5" t="inlineStr"/>
       <c r="I49" s="5" t="inlineStr">
         <is>
           <t>JCS</t>
         </is>
       </c>
-      <c r="J49" s="5" t="inlineStr">
-        <is>
-          <t>Certamen 1</t>
-        </is>
-      </c>
+      <c r="J49" s="5" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
@@ -2582,7 +2534,7 @@
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>Modelos y Derivadas 2</t>
+          <t>Modelos y Derivadas 3</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr"/>
@@ -2622,7 +2574,7 @@
       </c>
       <c r="G51" s="5" t="inlineStr">
         <is>
-          <t>Modelos y Derivadas 2</t>
+          <t>Modelos y Derivadas 3</t>
         </is>
       </c>
       <c r="H51" s="5" t="inlineStr"/>
@@ -2702,7 +2654,7 @@
       </c>
       <c r="G53" s="12" t="inlineStr">
         <is>
-          <t>Certamen 1</t>
+          <t>Sin Seminario</t>
         </is>
       </c>
       <c r="H53" s="12" t="inlineStr"/>
@@ -2746,7 +2698,7 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>Modelos y Derivadas 3</t>
+          <t>Modelos y Derivadas 4</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr"/>
@@ -2786,7 +2738,7 @@
       </c>
       <c r="G55" s="5" t="inlineStr">
         <is>
-          <t>Modelos y Derivadas 3</t>
+          <t>Revision Certamen</t>
         </is>
       </c>
       <c r="H55" s="5" t="inlineStr"/>
@@ -2826,7 +2778,7 @@
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>Modelos y Derivadas 4</t>
+          <t>Actividad Autónoma Portafolio</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr"/>
@@ -3109,21 +3061,13 @@
           <t>Linealización de modelos</t>
         </is>
       </c>
-      <c r="H63" s="8" t="inlineStr">
-        <is>
-          <t>Trabajo práctico</t>
-        </is>
-      </c>
+      <c r="H63" s="5" t="inlineStr"/>
       <c r="I63" s="5" t="inlineStr">
         <is>
           <t>JCS</t>
         </is>
       </c>
-      <c r="J63" s="5" t="inlineStr">
-        <is>
-          <t>Trabajo Práctico</t>
-        </is>
-      </c>
+      <c r="J63" s="5" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="2" t="n">
@@ -3357,21 +3301,13 @@
           <t>Trigonometría y Vectores 3</t>
         </is>
       </c>
-      <c r="H69" s="8" t="inlineStr">
-        <is>
-          <t>Control</t>
-        </is>
-      </c>
+      <c r="H69" s="5" t="inlineStr"/>
       <c r="I69" s="5" t="inlineStr">
         <is>
           <t>JCS</t>
         </is>
       </c>
-      <c r="J69" s="5" t="inlineStr">
-        <is>
-          <t>Taller Unidad 1 | Taller Unidad 2 | Taller Unidad 3</t>
-        </is>
-      </c>
+      <c r="J69" s="5" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="2" t="n">
@@ -3445,21 +3381,13 @@
           <t>Certamen 2</t>
         </is>
       </c>
-      <c r="H71" s="8" t="inlineStr">
-        <is>
-          <t>Certamen</t>
-        </is>
-      </c>
+      <c r="H71" s="5" t="inlineStr"/>
       <c r="I71" s="5" t="inlineStr">
         <is>
           <t>JCS</t>
         </is>
       </c>
-      <c r="J71" s="5" t="inlineStr">
-        <is>
-          <t>Certamen 2</t>
-        </is>
-      </c>
+      <c r="J71" s="5" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="9" t="n">
@@ -3621,21 +3549,13 @@
           <t>Examen Primera Oportunidad</t>
         </is>
       </c>
-      <c r="H75" s="8" t="inlineStr">
-        <is>
-          <t>Examen</t>
-        </is>
-      </c>
+      <c r="H75" s="5" t="inlineStr"/>
       <c r="I75" s="5" t="inlineStr">
         <is>
           <t>JCS</t>
         </is>
       </c>
-      <c r="J75" s="5" t="inlineStr">
-        <is>
-          <t>Examen 1</t>
-        </is>
-      </c>
+      <c r="J75" s="5" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="2" t="n">
@@ -3709,37 +3629,29 @@
           <t>Examen Segunda Oportunidad</t>
         </is>
       </c>
-      <c r="H77" s="8" t="inlineStr">
-        <is>
-          <t>Examen</t>
-        </is>
-      </c>
+      <c r="H77" s="5" t="inlineStr"/>
       <c r="I77" s="5" t="inlineStr">
         <is>
           <t>JCS</t>
         </is>
       </c>
-      <c r="J77" s="5" t="inlineStr">
-        <is>
-          <t>Examen 2</t>
-        </is>
-      </c>
+      <c r="J77" s="5" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="2" t="n">
         <v>1</v>
       </c>
       <c r="B78" s="3" t="n">
-        <v>46099</v>
+        <v>46098</v>
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>Miércoles</t>
+          <t>Martes</t>
         </is>
       </c>
       <c r="D78" s="4" t="inlineStr">
         <is>
-          <t>15:00–16:30</t>
+          <t>10:15–11:45</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
@@ -3770,16 +3682,16 @@
         <v>1</v>
       </c>
       <c r="B79" s="6" t="n">
-        <v>46100</v>
+        <v>46101</v>
       </c>
       <c r="C79" s="5" t="inlineStr">
         <is>
-          <t>Jueves</t>
+          <t>Viernes</t>
         </is>
       </c>
       <c r="D79" s="7" t="inlineStr">
         <is>
-          <t>08:30–10:00</t>
+          <t>15:00–16:30</t>
         </is>
       </c>
       <c r="E79" s="5" t="inlineStr">
@@ -3810,16 +3722,16 @@
         <v>2</v>
       </c>
       <c r="B80" s="3" t="n">
-        <v>46106</v>
+        <v>46105</v>
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>Miércoles</t>
+          <t>Martes</t>
         </is>
       </c>
       <c r="D80" s="4" t="inlineStr">
         <is>
-          <t>15:00–16:30</t>
+          <t>10:15–11:45</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
@@ -3850,16 +3762,16 @@
         <v>2</v>
       </c>
       <c r="B81" s="6" t="n">
-        <v>46107</v>
+        <v>46108</v>
       </c>
       <c r="C81" s="5" t="inlineStr">
         <is>
-          <t>Jueves</t>
+          <t>Viernes</t>
         </is>
       </c>
       <c r="D81" s="7" t="inlineStr">
         <is>
-          <t>08:30–10:00</t>
+          <t>15:00–16:30</t>
         </is>
       </c>
       <c r="E81" s="5" t="inlineStr">
@@ -3890,16 +3802,16 @@
         <v>3</v>
       </c>
       <c r="B82" s="3" t="n">
-        <v>46113</v>
+        <v>46112</v>
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>Miércoles</t>
+          <t>Martes</t>
         </is>
       </c>
       <c r="D82" s="4" t="inlineStr">
         <is>
-          <t>15:00–16:30</t>
+          <t>10:15–11:45</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
@@ -3914,7 +3826,7 @@
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>Lógica 3</t>
+          <t>Lógica 3 teórico-práctico</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr"/>
@@ -3926,60 +3838,64 @@
       <c r="J82" s="2" t="inlineStr"/>
     </row>
     <row r="83">
-      <c r="A83" s="5" t="n">
+      <c r="A83" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="B83" s="6" t="n">
-        <v>46114</v>
-      </c>
-      <c r="C83" s="5" t="inlineStr">
-        <is>
-          <t>Jueves</t>
-        </is>
-      </c>
-      <c r="D83" s="7" t="inlineStr">
-        <is>
-          <t>08:30–10:00</t>
-        </is>
-      </c>
-      <c r="E83" s="5" t="inlineStr">
+      <c r="B83" s="13" t="n">
+        <v>46115</v>
+      </c>
+      <c r="C83" s="12" t="inlineStr">
+        <is>
+          <t>Viernes</t>
+        </is>
+      </c>
+      <c r="D83" s="14" t="inlineStr">
+        <is>
+          <t>15:00–16:30</t>
+        </is>
+      </c>
+      <c r="E83" s="12" t="inlineStr">
         <is>
           <t>Sección 3</t>
         </is>
       </c>
-      <c r="F83" s="5" t="inlineStr">
-        <is>
-          <t>Seminario</t>
-        </is>
-      </c>
-      <c r="G83" s="5" t="inlineStr">
-        <is>
-          <t>Lógica 3</t>
-        </is>
-      </c>
-      <c r="H83" s="5" t="inlineStr"/>
-      <c r="I83" s="5" t="inlineStr">
-        <is>
-          <t>JCS</t>
-        </is>
-      </c>
-      <c r="J83" s="5" t="inlineStr"/>
+      <c r="F83" s="12" t="inlineStr">
+        <is>
+          <t>Sin clases (Feriado)</t>
+        </is>
+      </c>
+      <c r="G83" s="12" t="inlineStr">
+        <is>
+          <t>Sin Seminario</t>
+        </is>
+      </c>
+      <c r="H83" s="12" t="inlineStr"/>
+      <c r="I83" s="12" t="inlineStr">
+        <is>
+          <t>JCS</t>
+        </is>
+      </c>
+      <c r="J83" s="12" t="inlineStr">
+        <is>
+          <t>Viernes Santo</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="n">
         <v>4</v>
       </c>
       <c r="B84" s="3" t="n">
-        <v>46120</v>
+        <v>46119</v>
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>Miércoles</t>
+          <t>Martes</t>
         </is>
       </c>
       <c r="D84" s="4" t="inlineStr">
         <is>
-          <t>15:00–16:30</t>
+          <t>10:15–11:45</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr">
@@ -3994,7 +3910,7 @@
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>Repaso (semana mechona)</t>
+          <t>Modelos y Derivadas 1 teórico-práctico</t>
         </is>
       </c>
       <c r="H84" s="2" t="inlineStr"/>
@@ -4010,16 +3926,16 @@
         <v>4</v>
       </c>
       <c r="B85" s="6" t="n">
-        <v>46121</v>
+        <v>46122</v>
       </c>
       <c r="C85" s="5" t="inlineStr">
         <is>
-          <t>Jueves</t>
+          <t>Viernes</t>
         </is>
       </c>
       <c r="D85" s="7" t="inlineStr">
         <is>
-          <t>08:30–10:00</t>
+          <t>15:00–16:30</t>
         </is>
       </c>
       <c r="E85" s="5" t="inlineStr">
@@ -4034,7 +3950,7 @@
       </c>
       <c r="G85" s="5" t="inlineStr">
         <is>
-          <t>Repaso (semana mechona)</t>
+          <t>Sin Seminario (semana mechona)</t>
         </is>
       </c>
       <c r="H85" s="5" t="inlineStr"/>
@@ -4050,16 +3966,16 @@
         <v>5</v>
       </c>
       <c r="B86" s="3" t="n">
-        <v>46127</v>
+        <v>46126</v>
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>Miércoles</t>
+          <t>Martes</t>
         </is>
       </c>
       <c r="D86" s="4" t="inlineStr">
         <is>
-          <t>15:00–16:30</t>
+          <t>10:15–11:45</t>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr">
@@ -4074,7 +3990,7 @@
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>Modelos y Derivadas 1</t>
+          <t>Modelos y Derivadas 2</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr"/>
@@ -4090,16 +4006,16 @@
         <v>5</v>
       </c>
       <c r="B87" s="6" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="C87" s="5" t="inlineStr">
         <is>
-          <t>Jueves</t>
+          <t>Viernes</t>
         </is>
       </c>
       <c r="D87" s="7" t="inlineStr">
         <is>
-          <t>08:30–10:00</t>
+          <t>15:00–16:30</t>
         </is>
       </c>
       <c r="E87" s="5" t="inlineStr">
@@ -4114,40 +4030,32 @@
       </c>
       <c r="G87" s="5" t="inlineStr">
         <is>
-          <t>Modelos y Derivadas 1</t>
-        </is>
-      </c>
-      <c r="H87" s="8" t="inlineStr">
-        <is>
-          <t>Certamen</t>
-        </is>
-      </c>
+          <t>Modelos y Derivadas 2</t>
+        </is>
+      </c>
+      <c r="H87" s="5" t="inlineStr"/>
       <c r="I87" s="5" t="inlineStr">
         <is>
           <t>JCS</t>
         </is>
       </c>
-      <c r="J87" s="5" t="inlineStr">
-        <is>
-          <t>Certamen 1</t>
-        </is>
-      </c>
+      <c r="J87" s="5" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" s="2" t="n">
         <v>6</v>
       </c>
       <c r="B88" s="3" t="n">
-        <v>46134</v>
+        <v>46133</v>
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>Miércoles</t>
+          <t>Martes</t>
         </is>
       </c>
       <c r="D88" s="4" t="inlineStr">
         <is>
-          <t>15:00–16:30</t>
+          <t>10:15–11:45</t>
         </is>
       </c>
       <c r="E88" s="2" t="inlineStr">
@@ -4162,7 +4070,7 @@
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>Modelos y Derivadas 2</t>
+          <t>Modelos y Derivadas 3</t>
         </is>
       </c>
       <c r="H88" s="2" t="inlineStr"/>
@@ -4178,16 +4086,16 @@
         <v>6</v>
       </c>
       <c r="B89" s="6" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="C89" s="5" t="inlineStr">
         <is>
-          <t>Jueves</t>
+          <t>Viernes</t>
         </is>
       </c>
       <c r="D89" s="7" t="inlineStr">
         <is>
-          <t>08:30–10:00</t>
+          <t>15:00–16:30</t>
         </is>
       </c>
       <c r="E89" s="5" t="inlineStr">
@@ -4202,7 +4110,7 @@
       </c>
       <c r="G89" s="5" t="inlineStr">
         <is>
-          <t>Modelos y Derivadas 2</t>
+          <t>Modelos y Derivadas 3</t>
         </is>
       </c>
       <c r="H89" s="5" t="inlineStr"/>
@@ -4218,16 +4126,16 @@
         <v>7</v>
       </c>
       <c r="B90" s="3" t="n">
-        <v>46141</v>
+        <v>46140</v>
       </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>Miércoles</t>
+          <t>Martes</t>
         </is>
       </c>
       <c r="D90" s="4" t="inlineStr">
         <is>
-          <t>15:00–16:30</t>
+          <t>10:15–11:45</t>
         </is>
       </c>
       <c r="E90" s="2" t="inlineStr">
@@ -4254,60 +4162,64 @@
       <c r="J90" s="2" t="inlineStr"/>
     </row>
     <row r="91">
-      <c r="A91" s="5" t="n">
+      <c r="A91" s="12" t="n">
         <v>7</v>
       </c>
-      <c r="B91" s="6" t="n">
-        <v>46142</v>
-      </c>
-      <c r="C91" s="5" t="inlineStr">
-        <is>
-          <t>Jueves</t>
-        </is>
-      </c>
-      <c r="D91" s="7" t="inlineStr">
-        <is>
-          <t>08:30–10:00</t>
-        </is>
-      </c>
-      <c r="E91" s="5" t="inlineStr">
+      <c r="B91" s="13" t="n">
+        <v>46143</v>
+      </c>
+      <c r="C91" s="12" t="inlineStr">
+        <is>
+          <t>Viernes</t>
+        </is>
+      </c>
+      <c r="D91" s="14" t="inlineStr">
+        <is>
+          <t>15:00–16:30</t>
+        </is>
+      </c>
+      <c r="E91" s="12" t="inlineStr">
         <is>
           <t>Sección 3</t>
         </is>
       </c>
-      <c r="F91" s="5" t="inlineStr">
-        <is>
-          <t>Seminario</t>
-        </is>
-      </c>
-      <c r="G91" s="5" t="inlineStr">
-        <is>
-          <t>Certamen 1</t>
-        </is>
-      </c>
-      <c r="H91" s="5" t="inlineStr"/>
-      <c r="I91" s="5" t="inlineStr">
-        <is>
-          <t>JCS</t>
-        </is>
-      </c>
-      <c r="J91" s="5" t="inlineStr"/>
+      <c r="F91" s="12" t="inlineStr">
+        <is>
+          <t>Sin clases (Feriado)</t>
+        </is>
+      </c>
+      <c r="G91" s="12" t="inlineStr">
+        <is>
+          <t>Sin Seminario</t>
+        </is>
+      </c>
+      <c r="H91" s="12" t="inlineStr"/>
+      <c r="I91" s="12" t="inlineStr">
+        <is>
+          <t>JCS</t>
+        </is>
+      </c>
+      <c r="J91" s="12" t="inlineStr">
+        <is>
+          <t>Día Nacional del Trabajo</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="n">
         <v>8</v>
       </c>
       <c r="B92" s="3" t="n">
-        <v>46148</v>
+        <v>46147</v>
       </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>Miércoles</t>
+          <t>Martes</t>
         </is>
       </c>
       <c r="D92" s="4" t="inlineStr">
         <is>
-          <t>15:00–16:30</t>
+          <t>10:15–11:45</t>
         </is>
       </c>
       <c r="E92" s="2" t="inlineStr">
@@ -4322,7 +4234,7 @@
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>Modelos y Derivadas 3</t>
+          <t>Modelos y Derivadas 4</t>
         </is>
       </c>
       <c r="H92" s="2" t="inlineStr"/>
@@ -4338,16 +4250,16 @@
         <v>8</v>
       </c>
       <c r="B93" s="6" t="n">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="C93" s="5" t="inlineStr">
         <is>
-          <t>Jueves</t>
+          <t>Viernes</t>
         </is>
       </c>
       <c r="D93" s="7" t="inlineStr">
         <is>
-          <t>08:30–10:00</t>
+          <t>15:00–16:30</t>
         </is>
       </c>
       <c r="E93" s="5" t="inlineStr">
@@ -4362,7 +4274,7 @@
       </c>
       <c r="G93" s="5" t="inlineStr">
         <is>
-          <t>Modelos y Derivadas 3</t>
+          <t>Revision Certamen</t>
         </is>
       </c>
       <c r="H93" s="5" t="inlineStr"/>
@@ -4378,16 +4290,16 @@
         <v>9</v>
       </c>
       <c r="B94" s="3" t="n">
-        <v>46155</v>
+        <v>46154</v>
       </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>Miércoles</t>
+          <t>Martes</t>
         </is>
       </c>
       <c r="D94" s="4" t="inlineStr">
         <is>
-          <t>15:00–16:30</t>
+          <t>10:15–11:45</t>
         </is>
       </c>
       <c r="E94" s="2" t="inlineStr">
@@ -4402,7 +4314,7 @@
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>Modelos y Derivadas 4</t>
+          <t>Actividad Autónoma Portafolio</t>
         </is>
       </c>
       <c r="H94" s="2" t="inlineStr"/>
@@ -4418,16 +4330,16 @@
         <v>9</v>
       </c>
       <c r="B95" s="6" t="n">
-        <v>46156</v>
+        <v>46157</v>
       </c>
       <c r="C95" s="5" t="inlineStr">
         <is>
-          <t>Jueves</t>
+          <t>Viernes</t>
         </is>
       </c>
       <c r="D95" s="7" t="inlineStr">
         <is>
-          <t>08:30–10:00</t>
+          <t>15:00–16:30</t>
         </is>
       </c>
       <c r="E95" s="5" t="inlineStr">
@@ -4458,16 +4370,16 @@
         <v>10</v>
       </c>
       <c r="B96" s="3" t="n">
-        <v>46162</v>
+        <v>46161</v>
       </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>Miércoles</t>
+          <t>Martes</t>
         </is>
       </c>
       <c r="D96" s="4" t="inlineStr">
         <is>
-          <t>15:00–16:30</t>
+          <t>10:15–11:45</t>
         </is>
       </c>
       <c r="E96" s="2" t="inlineStr">
@@ -4494,64 +4406,60 @@
       <c r="J96" s="2" t="inlineStr"/>
     </row>
     <row r="97">
-      <c r="A97" s="12" t="n">
+      <c r="A97" s="5" t="n">
         <v>10</v>
       </c>
-      <c r="B97" s="13" t="n">
-        <v>46163</v>
-      </c>
-      <c r="C97" s="12" t="inlineStr">
-        <is>
-          <t>Jueves</t>
-        </is>
-      </c>
-      <c r="D97" s="14" t="inlineStr">
-        <is>
-          <t>08:30–10:00</t>
-        </is>
-      </c>
-      <c r="E97" s="12" t="inlineStr">
+      <c r="B97" s="6" t="n">
+        <v>46164</v>
+      </c>
+      <c r="C97" s="5" t="inlineStr">
+        <is>
+          <t>Viernes</t>
+        </is>
+      </c>
+      <c r="D97" s="7" t="inlineStr">
+        <is>
+          <t>15:00–16:30</t>
+        </is>
+      </c>
+      <c r="E97" s="5" t="inlineStr">
         <is>
           <t>Sección 3</t>
         </is>
       </c>
-      <c r="F97" s="12" t="inlineStr">
-        <is>
-          <t>Sin clases (Feriado)</t>
-        </is>
-      </c>
-      <c r="G97" s="12" t="inlineStr">
+      <c r="F97" s="5" t="inlineStr">
+        <is>
+          <t>Seminario</t>
+        </is>
+      </c>
+      <c r="G97" s="5" t="inlineStr">
         <is>
           <t>Semana Receso</t>
         </is>
       </c>
-      <c r="H97" s="12" t="inlineStr"/>
-      <c r="I97" s="12" t="inlineStr">
-        <is>
-          <t>JCS</t>
-        </is>
-      </c>
-      <c r="J97" s="12" t="inlineStr">
-        <is>
-          <t>Día de las Glorias Navales</t>
-        </is>
-      </c>
+      <c r="H97" s="5" t="inlineStr"/>
+      <c r="I97" s="5" t="inlineStr">
+        <is>
+          <t>JCS</t>
+        </is>
+      </c>
+      <c r="J97" s="5" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" s="2" t="n">
         <v>11</v>
       </c>
       <c r="B98" s="3" t="n">
-        <v>46169</v>
+        <v>46168</v>
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>Miércoles</t>
+          <t>Martes</t>
         </is>
       </c>
       <c r="D98" s="4" t="inlineStr">
         <is>
-          <t>15:00–16:30</t>
+          <t>10:15–11:45</t>
         </is>
       </c>
       <c r="E98" s="2" t="inlineStr">
@@ -4582,16 +4490,16 @@
         <v>11</v>
       </c>
       <c r="B99" s="6" t="n">
-        <v>46170</v>
+        <v>46171</v>
       </c>
       <c r="C99" s="5" t="inlineStr">
         <is>
-          <t>Jueves</t>
+          <t>Viernes</t>
         </is>
       </c>
       <c r="D99" s="7" t="inlineStr">
         <is>
-          <t>08:30–10:00</t>
+          <t>15:00–16:30</t>
         </is>
       </c>
       <c r="E99" s="5" t="inlineStr">
@@ -4622,16 +4530,16 @@
         <v>12</v>
       </c>
       <c r="B100" s="3" t="n">
-        <v>46176</v>
+        <v>46175</v>
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>Miércoles</t>
+          <t>Martes</t>
         </is>
       </c>
       <c r="D100" s="4" t="inlineStr">
         <is>
-          <t>15:00–16:30</t>
+          <t>10:15–11:45</t>
         </is>
       </c>
       <c r="E100" s="2" t="inlineStr">
@@ -4662,16 +4570,16 @@
         <v>12</v>
       </c>
       <c r="B101" s="6" t="n">
-        <v>46177</v>
+        <v>46178</v>
       </c>
       <c r="C101" s="5" t="inlineStr">
         <is>
-          <t>Jueves</t>
+          <t>Viernes</t>
         </is>
       </c>
       <c r="D101" s="7" t="inlineStr">
         <is>
-          <t>08:30–10:00</t>
+          <t>15:00–16:30</t>
         </is>
       </c>
       <c r="E101" s="5" t="inlineStr">
@@ -4689,37 +4597,29 @@
           <t>Linealización de modelos</t>
         </is>
       </c>
-      <c r="H101" s="8" t="inlineStr">
-        <is>
-          <t>Trabajo práctico</t>
-        </is>
-      </c>
+      <c r="H101" s="5" t="inlineStr"/>
       <c r="I101" s="5" t="inlineStr">
         <is>
           <t>JCS</t>
         </is>
       </c>
-      <c r="J101" s="5" t="inlineStr">
-        <is>
-          <t>Trabajo Práctico</t>
-        </is>
-      </c>
+      <c r="J101" s="5" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" s="2" t="n">
         <v>13</v>
       </c>
       <c r="B102" s="3" t="n">
-        <v>46183</v>
+        <v>46182</v>
       </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
-          <t>Miércoles</t>
+          <t>Martes</t>
         </is>
       </c>
       <c r="D102" s="4" t="inlineStr">
         <is>
-          <t>15:00–16:30</t>
+          <t>10:15–11:45</t>
         </is>
       </c>
       <c r="E102" s="2" t="inlineStr">
@@ -4750,16 +4650,16 @@
         <v>13</v>
       </c>
       <c r="B103" s="6" t="n">
-        <v>46184</v>
+        <v>46185</v>
       </c>
       <c r="C103" s="5" t="inlineStr">
         <is>
-          <t>Jueves</t>
+          <t>Viernes</t>
         </is>
       </c>
       <c r="D103" s="7" t="inlineStr">
         <is>
-          <t>08:30–10:00</t>
+          <t>15:00–16:30</t>
         </is>
       </c>
       <c r="E103" s="5" t="inlineStr">
@@ -4790,16 +4690,16 @@
         <v>14</v>
       </c>
       <c r="B104" s="3" t="n">
-        <v>46190</v>
+        <v>46189</v>
       </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
-          <t>Miércoles</t>
+          <t>Martes</t>
         </is>
       </c>
       <c r="D104" s="4" t="inlineStr">
         <is>
-          <t>15:00–16:30</t>
+          <t>10:15–11:45</t>
         </is>
       </c>
       <c r="E104" s="2" t="inlineStr">
@@ -4830,16 +4730,16 @@
         <v>14</v>
       </c>
       <c r="B105" s="6" t="n">
-        <v>46191</v>
+        <v>46192</v>
       </c>
       <c r="C105" s="5" t="inlineStr">
         <is>
-          <t>Jueves</t>
+          <t>Viernes</t>
         </is>
       </c>
       <c r="D105" s="7" t="inlineStr">
         <is>
-          <t>08:30–10:00</t>
+          <t>15:00–16:30</t>
         </is>
       </c>
       <c r="E105" s="5" t="inlineStr">
@@ -4870,16 +4770,16 @@
         <v>15</v>
       </c>
       <c r="B106" s="3" t="n">
-        <v>46197</v>
+        <v>46196</v>
       </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
-          <t>Miércoles</t>
+          <t>Martes</t>
         </is>
       </c>
       <c r="D106" s="4" t="inlineStr">
         <is>
-          <t>15:00–16:30</t>
+          <t>10:15–11:45</t>
         </is>
       </c>
       <c r="E106" s="2" t="inlineStr">
@@ -4910,16 +4810,16 @@
         <v>15</v>
       </c>
       <c r="B107" s="6" t="n">
-        <v>46198</v>
+        <v>46199</v>
       </c>
       <c r="C107" s="5" t="inlineStr">
         <is>
-          <t>Jueves</t>
+          <t>Viernes</t>
         </is>
       </c>
       <c r="D107" s="7" t="inlineStr">
         <is>
-          <t>08:30–10:00</t>
+          <t>15:00–16:30</t>
         </is>
       </c>
       <c r="E107" s="5" t="inlineStr">
@@ -4937,37 +4837,29 @@
           <t>Trigonometría y Vectores 3</t>
         </is>
       </c>
-      <c r="H107" s="8" t="inlineStr">
-        <is>
-          <t>Control</t>
-        </is>
-      </c>
+      <c r="H107" s="5" t="inlineStr"/>
       <c r="I107" s="5" t="inlineStr">
         <is>
           <t>JCS</t>
         </is>
       </c>
-      <c r="J107" s="5" t="inlineStr">
-        <is>
-          <t>Taller Unidad 1 | Taller Unidad 2 | Taller Unidad 3</t>
-        </is>
-      </c>
+      <c r="J107" s="5" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" s="2" t="n">
         <v>16</v>
       </c>
       <c r="B108" s="3" t="n">
-        <v>46204</v>
+        <v>46203</v>
       </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
-          <t>Miércoles</t>
+          <t>Martes</t>
         </is>
       </c>
       <c r="D108" s="4" t="inlineStr">
         <is>
-          <t>15:00–16:30</t>
+          <t>10:15–11:45</t>
         </is>
       </c>
       <c r="E108" s="2" t="inlineStr">
@@ -4998,16 +4890,16 @@
         <v>16</v>
       </c>
       <c r="B109" s="6" t="n">
-        <v>46205</v>
+        <v>46206</v>
       </c>
       <c r="C109" s="5" t="inlineStr">
         <is>
-          <t>Jueves</t>
+          <t>Viernes</t>
         </is>
       </c>
       <c r="D109" s="7" t="inlineStr">
         <is>
-          <t>08:30–10:00</t>
+          <t>15:00–16:30</t>
         </is>
       </c>
       <c r="E109" s="5" t="inlineStr">
@@ -5025,37 +4917,29 @@
           <t>Certamen 2</t>
         </is>
       </c>
-      <c r="H109" s="8" t="inlineStr">
-        <is>
-          <t>Certamen</t>
-        </is>
-      </c>
+      <c r="H109" s="5" t="inlineStr"/>
       <c r="I109" s="5" t="inlineStr">
         <is>
           <t>JCS</t>
         </is>
       </c>
-      <c r="J109" s="5" t="inlineStr">
-        <is>
-          <t>Certamen 2</t>
-        </is>
-      </c>
+      <c r="J109" s="5" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" s="9" t="n">
         <v>17</v>
       </c>
       <c r="B110" s="10" t="n">
-        <v>46211</v>
+        <v>46210</v>
       </c>
       <c r="C110" s="9" t="inlineStr">
         <is>
-          <t>Miércoles</t>
+          <t>Martes</t>
         </is>
       </c>
       <c r="D110" s="11" t="inlineStr">
         <is>
-          <t>15:00–16:30</t>
+          <t>10:15–11:45</t>
         </is>
       </c>
       <c r="E110" s="9" t="inlineStr">
@@ -5090,16 +4974,16 @@
         <v>17</v>
       </c>
       <c r="B111" s="10" t="n">
-        <v>46212</v>
+        <v>46213</v>
       </c>
       <c r="C111" s="9" t="inlineStr">
         <is>
-          <t>Jueves</t>
+          <t>Viernes</t>
         </is>
       </c>
       <c r="D111" s="11" t="inlineStr">
         <is>
-          <t>08:30–10:00</t>
+          <t>15:00–16:30</t>
         </is>
       </c>
       <c r="E111" s="9" t="inlineStr">
@@ -5134,16 +5018,16 @@
         <v>18</v>
       </c>
       <c r="B112" s="3" t="n">
-        <v>46218</v>
+        <v>46217</v>
       </c>
       <c r="C112" s="2" t="inlineStr">
         <is>
-          <t>Miércoles</t>
+          <t>Martes</t>
         </is>
       </c>
       <c r="D112" s="4" t="inlineStr">
         <is>
-          <t>15:00–16:30</t>
+          <t>10:15–11:45</t>
         </is>
       </c>
       <c r="E112" s="2" t="inlineStr">
@@ -5170,68 +5054,60 @@
       <c r="J112" s="2" t="inlineStr"/>
     </row>
     <row r="113">
-      <c r="A113" s="12" t="n">
+      <c r="A113" s="5" t="n">
         <v>18</v>
       </c>
-      <c r="B113" s="13" t="n">
-        <v>46219</v>
-      </c>
-      <c r="C113" s="12" t="inlineStr">
-        <is>
-          <t>Jueves</t>
-        </is>
-      </c>
-      <c r="D113" s="14" t="inlineStr">
-        <is>
-          <t>08:30–10:00</t>
-        </is>
-      </c>
-      <c r="E113" s="12" t="inlineStr">
+      <c r="B113" s="6" t="n">
+        <v>46220</v>
+      </c>
+      <c r="C113" s="5" t="inlineStr">
+        <is>
+          <t>Viernes</t>
+        </is>
+      </c>
+      <c r="D113" s="7" t="inlineStr">
+        <is>
+          <t>15:00–16:30</t>
+        </is>
+      </c>
+      <c r="E113" s="5" t="inlineStr">
         <is>
           <t>Sección 3</t>
         </is>
       </c>
-      <c r="F113" s="12" t="inlineStr">
-        <is>
-          <t>Sin clases (Feriado)</t>
-        </is>
-      </c>
-      <c r="G113" s="12" t="inlineStr">
+      <c r="F113" s="5" t="inlineStr">
+        <is>
+          <t>Seminario</t>
+        </is>
+      </c>
+      <c r="G113" s="5" t="inlineStr">
         <is>
           <t>Examen Primera Oportunidad</t>
         </is>
       </c>
-      <c r="H113" s="8" t="inlineStr">
-        <is>
-          <t>Examen</t>
-        </is>
-      </c>
-      <c r="I113" s="12" t="inlineStr">
-        <is>
-          <t>JCS</t>
-        </is>
-      </c>
-      <c r="J113" s="12" t="inlineStr">
-        <is>
-          <t>Virgen del Carmen</t>
-        </is>
-      </c>
+      <c r="H113" s="5" t="inlineStr"/>
+      <c r="I113" s="5" t="inlineStr">
+        <is>
+          <t>JCS</t>
+        </is>
+      </c>
+      <c r="J113" s="5" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" s="2" t="n">
         <v>19</v>
       </c>
       <c r="B114" s="3" t="n">
-        <v>46225</v>
+        <v>46224</v>
       </c>
       <c r="C114" s="2" t="inlineStr">
         <is>
-          <t>Miércoles</t>
+          <t>Martes</t>
         </is>
       </c>
       <c r="D114" s="4" t="inlineStr">
         <is>
-          <t>15:00–16:30</t>
+          <t>10:15–11:45</t>
         </is>
       </c>
       <c r="E114" s="2" t="inlineStr">
@@ -5262,16 +5138,16 @@
         <v>19</v>
       </c>
       <c r="B115" s="6" t="n">
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="C115" s="5" t="inlineStr">
         <is>
-          <t>Jueves</t>
+          <t>Viernes</t>
         </is>
       </c>
       <c r="D115" s="7" t="inlineStr">
         <is>
-          <t>08:30–10:00</t>
+          <t>15:00–16:30</t>
         </is>
       </c>
       <c r="E115" s="5" t="inlineStr">
@@ -5289,21 +5165,13 @@
           <t>Examen Segunda Oportunidad</t>
         </is>
       </c>
-      <c r="H115" s="8" t="inlineStr">
-        <is>
-          <t>Examen</t>
-        </is>
-      </c>
+      <c r="H115" s="5" t="inlineStr"/>
       <c r="I115" s="5" t="inlineStr">
         <is>
           <t>JCS</t>
         </is>
       </c>
-      <c r="J115" s="5" t="inlineStr">
-        <is>
-          <t>Examen 2</t>
-        </is>
-      </c>
+      <c r="J115" s="5" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" s="2" t="n">
@@ -5494,7 +5362,7 @@
       </c>
       <c r="G120" s="2" t="inlineStr">
         <is>
-          <t>Lógica 3</t>
+          <t>Lógica 3 teórico-práctico</t>
         </is>
       </c>
       <c r="H120" s="2" t="inlineStr"/>
@@ -5534,7 +5402,7 @@
       </c>
       <c r="G121" s="12" t="inlineStr">
         <is>
-          <t>Lógica 3</t>
+          <t>Sin Seminario</t>
         </is>
       </c>
       <c r="H121" s="12" t="inlineStr"/>
@@ -5578,7 +5446,7 @@
       </c>
       <c r="G122" s="2" t="inlineStr">
         <is>
-          <t>Repaso (semana mechona)</t>
+          <t>Modelos y Derivadas 1 teórico-práctico</t>
         </is>
       </c>
       <c r="H122" s="2" t="inlineStr"/>
@@ -5618,7 +5486,7 @@
       </c>
       <c r="G123" s="5" t="inlineStr">
         <is>
-          <t>Repaso (semana mechona)</t>
+          <t>Sin Seminario (semana mechona)</t>
         </is>
       </c>
       <c r="H123" s="5" t="inlineStr"/>
@@ -5658,7 +5526,7 @@
       </c>
       <c r="G124" s="2" t="inlineStr">
         <is>
-          <t>Modelos y Derivadas 1</t>
+          <t>Modelos y Derivadas 2</t>
         </is>
       </c>
       <c r="H124" s="2" t="inlineStr"/>
@@ -5698,24 +5566,16 @@
       </c>
       <c r="G125" s="5" t="inlineStr">
         <is>
-          <t>Modelos y Derivadas 1</t>
-        </is>
-      </c>
-      <c r="H125" s="8" t="inlineStr">
-        <is>
-          <t>Certamen</t>
-        </is>
-      </c>
+          <t>Modelos y Derivadas 2</t>
+        </is>
+      </c>
+      <c r="H125" s="5" t="inlineStr"/>
       <c r="I125" s="5" t="inlineStr">
         <is>
           <t>JCS</t>
         </is>
       </c>
-      <c r="J125" s="5" t="inlineStr">
-        <is>
-          <t>Certamen 1</t>
-        </is>
-      </c>
+      <c r="J125" s="5" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" s="2" t="n">
@@ -5746,7 +5606,7 @@
       </c>
       <c r="G126" s="2" t="inlineStr">
         <is>
-          <t>Modelos y Derivadas 2</t>
+          <t>Modelos y Derivadas 3</t>
         </is>
       </c>
       <c r="H126" s="2" t="inlineStr"/>
@@ -5786,7 +5646,7 @@
       </c>
       <c r="G127" s="5" t="inlineStr">
         <is>
-          <t>Modelos y Derivadas 2</t>
+          <t>Modelos y Derivadas 3</t>
         </is>
       </c>
       <c r="H127" s="5" t="inlineStr"/>
@@ -5866,7 +5726,7 @@
       </c>
       <c r="G129" s="12" t="inlineStr">
         <is>
-          <t>Certamen 1</t>
+          <t>Sin Seminario</t>
         </is>
       </c>
       <c r="H129" s="12" t="inlineStr"/>
@@ -5910,7 +5770,7 @@
       </c>
       <c r="G130" s="2" t="inlineStr">
         <is>
-          <t>Modelos y Derivadas 3</t>
+          <t>Modelos y Derivadas 4</t>
         </is>
       </c>
       <c r="H130" s="2" t="inlineStr"/>
@@ -5950,7 +5810,7 @@
       </c>
       <c r="G131" s="5" t="inlineStr">
         <is>
-          <t>Modelos y Derivadas 3</t>
+          <t>Revision Certamen</t>
         </is>
       </c>
       <c r="H131" s="5" t="inlineStr"/>
@@ -5990,7 +5850,7 @@
       </c>
       <c r="G132" s="2" t="inlineStr">
         <is>
-          <t>Modelos y Derivadas 4</t>
+          <t>Actividad Autónoma Portafolio</t>
         </is>
       </c>
       <c r="H132" s="2" t="inlineStr"/>
@@ -6273,21 +6133,13 @@
           <t>Linealización de modelos</t>
         </is>
       </c>
-      <c r="H139" s="8" t="inlineStr">
-        <is>
-          <t>Trabajo práctico</t>
-        </is>
-      </c>
+      <c r="H139" s="5" t="inlineStr"/>
       <c r="I139" s="5" t="inlineStr">
         <is>
           <t>JCS</t>
         </is>
       </c>
-      <c r="J139" s="5" t="inlineStr">
-        <is>
-          <t>Trabajo Práctico</t>
-        </is>
-      </c>
+      <c r="J139" s="5" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" s="2" t="n">
@@ -6521,21 +6373,13 @@
           <t>Trigonometría y Vectores 3</t>
         </is>
       </c>
-      <c r="H145" s="8" t="inlineStr">
-        <is>
-          <t>Control</t>
-        </is>
-      </c>
+      <c r="H145" s="5" t="inlineStr"/>
       <c r="I145" s="5" t="inlineStr">
         <is>
           <t>JCS</t>
         </is>
       </c>
-      <c r="J145" s="5" t="inlineStr">
-        <is>
-          <t>Taller Unidad 1 | Taller Unidad 2 | Taller Unidad 3</t>
-        </is>
-      </c>
+      <c r="J145" s="5" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" s="2" t="n">
@@ -6609,21 +6453,13 @@
           <t>Certamen 2</t>
         </is>
       </c>
-      <c r="H147" s="8" t="inlineStr">
-        <is>
-          <t>Certamen</t>
-        </is>
-      </c>
+      <c r="H147" s="5" t="inlineStr"/>
       <c r="I147" s="5" t="inlineStr">
         <is>
           <t>JCS</t>
         </is>
       </c>
-      <c r="J147" s="5" t="inlineStr">
-        <is>
-          <t>Certamen 2</t>
-        </is>
-      </c>
+      <c r="J147" s="5" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" s="9" t="n">
@@ -6785,21 +6621,13 @@
           <t>Examen Primera Oportunidad</t>
         </is>
       </c>
-      <c r="H151" s="8" t="inlineStr">
-        <is>
-          <t>Examen</t>
-        </is>
-      </c>
+      <c r="H151" s="5" t="inlineStr"/>
       <c r="I151" s="5" t="inlineStr">
         <is>
           <t>JCS</t>
         </is>
       </c>
-      <c r="J151" s="5" t="inlineStr">
-        <is>
-          <t>Examen 1</t>
-        </is>
-      </c>
+      <c r="J151" s="5" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" s="2" t="n">
@@ -6873,21 +6701,13 @@
           <t>Examen Segunda Oportunidad</t>
         </is>
       </c>
-      <c r="H153" s="8" t="inlineStr">
-        <is>
-          <t>Examen</t>
-        </is>
-      </c>
+      <c r="H153" s="5" t="inlineStr"/>
       <c r="I153" s="5" t="inlineStr">
         <is>
           <t>JCS</t>
         </is>
       </c>
-      <c r="J153" s="5" t="inlineStr">
-        <is>
-          <t>Examen 2</t>
-        </is>
-      </c>
+      <c r="J153" s="5" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:J153"/>

--- a/data/enobnu/calendario.xlsx
+++ b/data/enobnu/calendario.xlsx
@@ -504,7 +504,7 @@
     <col width="11" customWidth="1" min="5" max="5"/>
     <col width="22" customWidth="1" min="6" max="6"/>
     <col width="40" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
     <col width="35" customWidth="1" min="10" max="10"/>
   </cols>
@@ -713,13 +713,21 @@
           <t>Lógica 2</t>
         </is>
       </c>
-      <c r="H5" s="5" t="inlineStr"/>
+      <c r="H5" s="8" t="inlineStr">
+        <is>
+          <t>Control</t>
+        </is>
+      </c>
       <c r="I5" s="5" t="inlineStr">
         <is>
           <t>JCS</t>
         </is>
       </c>
-      <c r="J5" s="5" t="inlineStr"/>
+      <c r="J5" s="5" t="inlineStr">
+        <is>
+          <t>Taller Unidad 1</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
@@ -1077,13 +1085,21 @@
           <t>Certamen 1</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr"/>
+      <c r="H14" s="8" t="inlineStr">
+        <is>
+          <t>Certamen</t>
+        </is>
+      </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
           <t>AR</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr"/>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>Certamen 1</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="n">
@@ -1194,7 +1210,7 @@
       </c>
       <c r="G17" s="5" t="inlineStr">
         <is>
-          <t>Revision Certamen</t>
+          <t>Revisión Certamen 1</t>
         </is>
       </c>
       <c r="H17" s="5" t="inlineStr"/>
@@ -1277,13 +1293,21 @@
           <t>Modelos y Derivadas 4</t>
         </is>
       </c>
-      <c r="H19" s="5" t="inlineStr"/>
+      <c r="H19" s="8" t="inlineStr">
+        <is>
+          <t>Control</t>
+        </is>
+      </c>
       <c r="I19" s="5" t="inlineStr">
         <is>
           <t>JCS</t>
         </is>
       </c>
-      <c r="J19" s="5" t="inlineStr"/>
+      <c r="J19" s="5" t="inlineStr">
+        <is>
+          <t>Taller Unidad 2</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
@@ -1517,13 +1541,21 @@
           <t>Linealización de modelos</t>
         </is>
       </c>
-      <c r="H25" s="5" t="inlineStr"/>
+      <c r="H25" s="8" t="inlineStr">
+        <is>
+          <t>Trabajo práctico</t>
+        </is>
+      </c>
       <c r="I25" s="5" t="inlineStr">
         <is>
           <t>JCS</t>
         </is>
       </c>
-      <c r="J25" s="5" t="inlineStr"/>
+      <c r="J25" s="5" t="inlineStr">
+        <is>
+          <t>Trabajo Práctico</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
@@ -1677,13 +1709,21 @@
           <t>Trigonometría y Vectores 2</t>
         </is>
       </c>
-      <c r="H29" s="5" t="inlineStr"/>
+      <c r="H29" s="8" t="inlineStr">
+        <is>
+          <t>Control</t>
+        </is>
+      </c>
       <c r="I29" s="5" t="inlineStr">
         <is>
           <t>JCS</t>
         </is>
       </c>
-      <c r="J29" s="5" t="inlineStr"/>
+      <c r="J29" s="5" t="inlineStr">
+        <is>
+          <t>Taller Unidad 3</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
@@ -1717,21 +1757,13 @@
           <t>Trigonometría y Vectores 3</t>
         </is>
       </c>
-      <c r="H30" s="8" t="inlineStr">
-        <is>
-          <t>Control</t>
-        </is>
-      </c>
+      <c r="H30" s="2" t="inlineStr"/>
       <c r="I30" s="2" t="inlineStr">
         <is>
           <t>AR</t>
         </is>
       </c>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>Taller Unidad 1</t>
-        </is>
-      </c>
+      <c r="J30" s="2" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="5" t="n">
@@ -1805,13 +1837,21 @@
           <t>Certamen 2</t>
         </is>
       </c>
-      <c r="H32" s="2" t="inlineStr"/>
+      <c r="H32" s="8" t="inlineStr">
+        <is>
+          <t>Certamen</t>
+        </is>
+      </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
           <t>AR</t>
         </is>
       </c>
-      <c r="J32" s="2" t="inlineStr"/>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
+          <t>Certamen 2</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="5" t="n">
@@ -1842,7 +1882,7 @@
       </c>
       <c r="G33" s="5" t="inlineStr">
         <is>
-          <t>Certamen 2</t>
+          <t>Revisión Certamen 2</t>
         </is>
       </c>
       <c r="H33" s="5" t="inlineStr"/>
@@ -1973,13 +2013,21 @@
           <t>Examen Primera Oportunidad</t>
         </is>
       </c>
-      <c r="H36" s="2" t="inlineStr"/>
+      <c r="H36" s="8" t="inlineStr">
+        <is>
+          <t>Examen</t>
+        </is>
+      </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
           <t>AR</t>
         </is>
       </c>
-      <c r="J36" s="2" t="inlineStr"/>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
+          <t>Examen 1</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="5" t="n">
@@ -2053,13 +2101,21 @@
           <t>Examen Segunda Oportunidad</t>
         </is>
       </c>
-      <c r="H38" s="2" t="inlineStr"/>
+      <c r="H38" s="8" t="inlineStr">
+        <is>
+          <t>Examen</t>
+        </is>
+      </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
           <t>AR</t>
         </is>
       </c>
-      <c r="J38" s="2" t="inlineStr"/>
+      <c r="J38" s="2" t="inlineStr">
+        <is>
+          <t>Examen 2</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="5" t="n">
@@ -2253,13 +2309,21 @@
           <t>Lógica 2</t>
         </is>
       </c>
-      <c r="H43" s="5" t="inlineStr"/>
+      <c r="H43" s="8" t="inlineStr">
+        <is>
+          <t>Control</t>
+        </is>
+      </c>
       <c r="I43" s="5" t="inlineStr">
         <is>
           <t>JCS</t>
         </is>
       </c>
-      <c r="J43" s="5" t="inlineStr"/>
+      <c r="J43" s="5" t="inlineStr">
+        <is>
+          <t>Taller Unidad 1</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
@@ -2617,13 +2681,21 @@
           <t>Certamen 1</t>
         </is>
       </c>
-      <c r="H52" s="2" t="inlineStr"/>
+      <c r="H52" s="8" t="inlineStr">
+        <is>
+          <t>Certamen</t>
+        </is>
+      </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
           <t>AR</t>
         </is>
       </c>
-      <c r="J52" s="2" t="inlineStr"/>
+      <c r="J52" s="2" t="inlineStr">
+        <is>
+          <t>Certamen 1</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="12" t="n">
@@ -2738,7 +2810,7 @@
       </c>
       <c r="G55" s="5" t="inlineStr">
         <is>
-          <t>Revision Certamen</t>
+          <t>Revisión Certamen 1</t>
         </is>
       </c>
       <c r="H55" s="5" t="inlineStr"/>
@@ -2821,13 +2893,21 @@
           <t>Modelos y Derivadas 4</t>
         </is>
       </c>
-      <c r="H57" s="5" t="inlineStr"/>
+      <c r="H57" s="8" t="inlineStr">
+        <is>
+          <t>Control</t>
+        </is>
+      </c>
       <c r="I57" s="5" t="inlineStr">
         <is>
           <t>JCS</t>
         </is>
       </c>
-      <c r="J57" s="5" t="inlineStr"/>
+      <c r="J57" s="5" t="inlineStr">
+        <is>
+          <t>Taller Unidad 2</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="n">
@@ -3061,13 +3141,21 @@
           <t>Linealización de modelos</t>
         </is>
       </c>
-      <c r="H63" s="5" t="inlineStr"/>
+      <c r="H63" s="8" t="inlineStr">
+        <is>
+          <t>Trabajo práctico</t>
+        </is>
+      </c>
       <c r="I63" s="5" t="inlineStr">
         <is>
           <t>JCS</t>
         </is>
       </c>
-      <c r="J63" s="5" t="inlineStr"/>
+      <c r="J63" s="5" t="inlineStr">
+        <is>
+          <t>Trabajo Práctico</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="n">
@@ -3221,13 +3309,21 @@
           <t>Trigonometría y Vectores 2</t>
         </is>
       </c>
-      <c r="H67" s="5" t="inlineStr"/>
+      <c r="H67" s="8" t="inlineStr">
+        <is>
+          <t>Control</t>
+        </is>
+      </c>
       <c r="I67" s="5" t="inlineStr">
         <is>
           <t>JCS</t>
         </is>
       </c>
-      <c r="J67" s="5" t="inlineStr"/>
+      <c r="J67" s="5" t="inlineStr">
+        <is>
+          <t>Taller Unidad 3</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="n">
@@ -3341,13 +3437,21 @@
           <t>Certamen 2</t>
         </is>
       </c>
-      <c r="H70" s="2" t="inlineStr"/>
+      <c r="H70" s="8" t="inlineStr">
+        <is>
+          <t>Certamen</t>
+        </is>
+      </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
           <t>AR</t>
         </is>
       </c>
-      <c r="J70" s="2" t="inlineStr"/>
+      <c r="J70" s="2" t="inlineStr">
+        <is>
+          <t>Certamen 2</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="5" t="n">
@@ -3378,7 +3482,7 @@
       </c>
       <c r="G71" s="5" t="inlineStr">
         <is>
-          <t>Certamen 2</t>
+          <t>Revisión Certamen 2</t>
         </is>
       </c>
       <c r="H71" s="5" t="inlineStr"/>
@@ -3509,13 +3613,21 @@
           <t>Examen Primera Oportunidad</t>
         </is>
       </c>
-      <c r="H74" s="2" t="inlineStr"/>
+      <c r="H74" s="8" t="inlineStr">
+        <is>
+          <t>Examen</t>
+        </is>
+      </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
           <t>AR</t>
         </is>
       </c>
-      <c r="J74" s="2" t="inlineStr"/>
+      <c r="J74" s="2" t="inlineStr">
+        <is>
+          <t>Examen 1</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="5" t="n">
@@ -3589,13 +3701,21 @@
           <t>Examen Segunda Oportunidad</t>
         </is>
       </c>
-      <c r="H76" s="2" t="inlineStr"/>
+      <c r="H76" s="8" t="inlineStr">
+        <is>
+          <t>Examen</t>
+        </is>
+      </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
           <t>AR</t>
         </is>
       </c>
-      <c r="J76" s="2" t="inlineStr"/>
+      <c r="J76" s="2" t="inlineStr">
+        <is>
+          <t>Examen 2</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="5" t="n">
@@ -3789,13 +3909,21 @@
           <t>Lógica 2</t>
         </is>
       </c>
-      <c r="H81" s="5" t="inlineStr"/>
+      <c r="H81" s="8" t="inlineStr">
+        <is>
+          <t>Control</t>
+        </is>
+      </c>
       <c r="I81" s="5" t="inlineStr">
         <is>
           <t>JCS</t>
         </is>
       </c>
-      <c r="J81" s="5" t="inlineStr"/>
+      <c r="J81" s="5" t="inlineStr">
+        <is>
+          <t>Taller Unidad 1</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="n">
@@ -4153,13 +4281,21 @@
           <t>Certamen 1</t>
         </is>
       </c>
-      <c r="H90" s="2" t="inlineStr"/>
+      <c r="H90" s="8" t="inlineStr">
+        <is>
+          <t>Certamen</t>
+        </is>
+      </c>
       <c r="I90" s="2" t="inlineStr">
         <is>
           <t>AR</t>
         </is>
       </c>
-      <c r="J90" s="2" t="inlineStr"/>
+      <c r="J90" s="2" t="inlineStr">
+        <is>
+          <t>Certamen 1</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="12" t="n">
@@ -4274,7 +4410,7 @@
       </c>
       <c r="G93" s="5" t="inlineStr">
         <is>
-          <t>Revision Certamen</t>
+          <t>Revisión Certamen 1</t>
         </is>
       </c>
       <c r="H93" s="5" t="inlineStr"/>
@@ -4357,13 +4493,21 @@
           <t>Modelos y Derivadas 4</t>
         </is>
       </c>
-      <c r="H95" s="5" t="inlineStr"/>
+      <c r="H95" s="8" t="inlineStr">
+        <is>
+          <t>Control</t>
+        </is>
+      </c>
       <c r="I95" s="5" t="inlineStr">
         <is>
           <t>JCS</t>
         </is>
       </c>
-      <c r="J95" s="5" t="inlineStr"/>
+      <c r="J95" s="5" t="inlineStr">
+        <is>
+          <t>Taller Unidad 2</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="n">
@@ -4597,13 +4741,21 @@
           <t>Linealización de modelos</t>
         </is>
       </c>
-      <c r="H101" s="5" t="inlineStr"/>
+      <c r="H101" s="8" t="inlineStr">
+        <is>
+          <t>Trabajo práctico</t>
+        </is>
+      </c>
       <c r="I101" s="5" t="inlineStr">
         <is>
           <t>JCS</t>
         </is>
       </c>
-      <c r="J101" s="5" t="inlineStr"/>
+      <c r="J101" s="5" t="inlineStr">
+        <is>
+          <t>Trabajo Práctico</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="n">
@@ -4757,13 +4909,21 @@
           <t>Trigonometría y Vectores 2</t>
         </is>
       </c>
-      <c r="H105" s="5" t="inlineStr"/>
+      <c r="H105" s="8" t="inlineStr">
+        <is>
+          <t>Control</t>
+        </is>
+      </c>
       <c r="I105" s="5" t="inlineStr">
         <is>
           <t>JCS</t>
         </is>
       </c>
-      <c r="J105" s="5" t="inlineStr"/>
+      <c r="J105" s="5" t="inlineStr">
+        <is>
+          <t>Taller Unidad 3</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="n">
@@ -4877,13 +5037,21 @@
           <t>Certamen 2</t>
         </is>
       </c>
-      <c r="H108" s="2" t="inlineStr"/>
+      <c r="H108" s="8" t="inlineStr">
+        <is>
+          <t>Certamen</t>
+        </is>
+      </c>
       <c r="I108" s="2" t="inlineStr">
         <is>
           <t>AR</t>
         </is>
       </c>
-      <c r="J108" s="2" t="inlineStr"/>
+      <c r="J108" s="2" t="inlineStr">
+        <is>
+          <t>Certamen 2</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" s="5" t="n">
@@ -4914,7 +5082,7 @@
       </c>
       <c r="G109" s="5" t="inlineStr">
         <is>
-          <t>Certamen 2</t>
+          <t>Revisión Certamen 2</t>
         </is>
       </c>
       <c r="H109" s="5" t="inlineStr"/>
@@ -5045,13 +5213,21 @@
           <t>Examen Primera Oportunidad</t>
         </is>
       </c>
-      <c r="H112" s="2" t="inlineStr"/>
+      <c r="H112" s="8" t="inlineStr">
+        <is>
+          <t>Examen</t>
+        </is>
+      </c>
       <c r="I112" s="2" t="inlineStr">
         <is>
           <t>AR</t>
         </is>
       </c>
-      <c r="J112" s="2" t="inlineStr"/>
+      <c r="J112" s="2" t="inlineStr">
+        <is>
+          <t>Examen 1</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" s="5" t="n">
@@ -5125,13 +5301,21 @@
           <t>Examen Segunda Oportunidad</t>
         </is>
       </c>
-      <c r="H114" s="2" t="inlineStr"/>
+      <c r="H114" s="8" t="inlineStr">
+        <is>
+          <t>Examen</t>
+        </is>
+      </c>
       <c r="I114" s="2" t="inlineStr">
         <is>
           <t>AR</t>
         </is>
       </c>
-      <c r="J114" s="2" t="inlineStr"/>
+      <c r="J114" s="2" t="inlineStr">
+        <is>
+          <t>Examen 2</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" s="5" t="n">
@@ -5325,13 +5509,21 @@
           <t>Lógica 2</t>
         </is>
       </c>
-      <c r="H119" s="5" t="inlineStr"/>
+      <c r="H119" s="8" t="inlineStr">
+        <is>
+          <t>Control</t>
+        </is>
+      </c>
       <c r="I119" s="5" t="inlineStr">
         <is>
           <t>JCS</t>
         </is>
       </c>
-      <c r="J119" s="5" t="inlineStr"/>
+      <c r="J119" s="5" t="inlineStr">
+        <is>
+          <t>Taller Unidad 1</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="n">
@@ -5689,13 +5881,21 @@
           <t>Certamen 1</t>
         </is>
       </c>
-      <c r="H128" s="2" t="inlineStr"/>
+      <c r="H128" s="8" t="inlineStr">
+        <is>
+          <t>Certamen</t>
+        </is>
+      </c>
       <c r="I128" s="2" t="inlineStr">
         <is>
           <t>AR</t>
         </is>
       </c>
-      <c r="J128" s="2" t="inlineStr"/>
+      <c r="J128" s="2" t="inlineStr">
+        <is>
+          <t>Certamen 1</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" s="12" t="n">
@@ -5810,7 +6010,7 @@
       </c>
       <c r="G131" s="5" t="inlineStr">
         <is>
-          <t>Revision Certamen</t>
+          <t>Revisión Certamen 1</t>
         </is>
       </c>
       <c r="H131" s="5" t="inlineStr"/>
@@ -5893,13 +6093,21 @@
           <t>Modelos y Derivadas 4</t>
         </is>
       </c>
-      <c r="H133" s="5" t="inlineStr"/>
+      <c r="H133" s="8" t="inlineStr">
+        <is>
+          <t>Control</t>
+        </is>
+      </c>
       <c r="I133" s="5" t="inlineStr">
         <is>
           <t>JCS</t>
         </is>
       </c>
-      <c r="J133" s="5" t="inlineStr"/>
+      <c r="J133" s="5" t="inlineStr">
+        <is>
+          <t>Taller Unidad 2</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" s="2" t="n">
@@ -6133,13 +6341,21 @@
           <t>Linealización de modelos</t>
         </is>
       </c>
-      <c r="H139" s="5" t="inlineStr"/>
+      <c r="H139" s="8" t="inlineStr">
+        <is>
+          <t>Trabajo práctico</t>
+        </is>
+      </c>
       <c r="I139" s="5" t="inlineStr">
         <is>
           <t>JCS</t>
         </is>
       </c>
-      <c r="J139" s="5" t="inlineStr"/>
+      <c r="J139" s="5" t="inlineStr">
+        <is>
+          <t>Trabajo Práctico</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" s="2" t="n">
@@ -6293,13 +6509,21 @@
           <t>Trigonometría y Vectores 2</t>
         </is>
       </c>
-      <c r="H143" s="5" t="inlineStr"/>
+      <c r="H143" s="8" t="inlineStr">
+        <is>
+          <t>Control</t>
+        </is>
+      </c>
       <c r="I143" s="5" t="inlineStr">
         <is>
           <t>JCS</t>
         </is>
       </c>
-      <c r="J143" s="5" t="inlineStr"/>
+      <c r="J143" s="5" t="inlineStr">
+        <is>
+          <t>Taller Unidad 3</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" s="2" t="n">
@@ -6413,13 +6637,21 @@
           <t>Certamen 2</t>
         </is>
       </c>
-      <c r="H146" s="2" t="inlineStr"/>
+      <c r="H146" s="8" t="inlineStr">
+        <is>
+          <t>Certamen</t>
+        </is>
+      </c>
       <c r="I146" s="2" t="inlineStr">
         <is>
           <t>AR</t>
         </is>
       </c>
-      <c r="J146" s="2" t="inlineStr"/>
+      <c r="J146" s="2" t="inlineStr">
+        <is>
+          <t>Certamen 2</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" s="5" t="n">
@@ -6450,7 +6682,7 @@
       </c>
       <c r="G147" s="5" t="inlineStr">
         <is>
-          <t>Certamen 2</t>
+          <t>Revisión Certamen 2</t>
         </is>
       </c>
       <c r="H147" s="5" t="inlineStr"/>
@@ -6581,13 +6813,21 @@
           <t>Examen Primera Oportunidad</t>
         </is>
       </c>
-      <c r="H150" s="2" t="inlineStr"/>
+      <c r="H150" s="8" t="inlineStr">
+        <is>
+          <t>Examen</t>
+        </is>
+      </c>
       <c r="I150" s="2" t="inlineStr">
         <is>
           <t>AR</t>
         </is>
       </c>
-      <c r="J150" s="2" t="inlineStr"/>
+      <c r="J150" s="2" t="inlineStr">
+        <is>
+          <t>Examen 1</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" s="5" t="n">
@@ -6661,13 +6901,21 @@
           <t>Examen Segunda Oportunidad</t>
         </is>
       </c>
-      <c r="H152" s="2" t="inlineStr"/>
+      <c r="H152" s="8" t="inlineStr">
+        <is>
+          <t>Examen</t>
+        </is>
+      </c>
       <c r="I152" s="2" t="inlineStr">
         <is>
           <t>AR</t>
         </is>
       </c>
-      <c r="J152" s="2" t="inlineStr"/>
+      <c r="J152" s="2" t="inlineStr">
+        <is>
+          <t>Examen 2</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" s="5" t="n">

--- a/data/enobnu/calendario.xlsx
+++ b/data/enobnu/calendario.xlsx
@@ -2438,7 +2438,7 @@
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>Sin Clase (semana mechona)</t>
+          <t>Modelos y Derivadas 1 teórico-práctico</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr"/>
@@ -2478,7 +2478,7 @@
       </c>
       <c r="G47" s="5" t="inlineStr">
         <is>
-          <t>Modelos y Derivadas 1 teórico-práctico</t>
+          <t>Sin Seminario (semana mechona)</t>
         </is>
       </c>
       <c r="H47" s="5" t="inlineStr"/>

--- a/data/enobnu/calendario.xlsx
+++ b/data/enobnu/calendario.xlsx
@@ -596,7 +596,7 @@
       <c r="H2" s="2" t="inlineStr"/>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>JCS</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr"/>
@@ -636,7 +636,7 @@
       <c r="H3" s="5" t="inlineStr"/>
       <c r="I3" s="5" t="inlineStr">
         <is>
-          <t>JCS</t>
+          <t>JM, MB, VB</t>
         </is>
       </c>
       <c r="J3" s="5" t="inlineStr"/>
@@ -676,7 +676,7 @@
       <c r="H4" s="2" t="inlineStr"/>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>JCS</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr"/>
@@ -720,7 +720,7 @@
       </c>
       <c r="I5" s="5" t="inlineStr">
         <is>
-          <t>JCS</t>
+          <t>JM, MB, VB</t>
         </is>
       </c>
       <c r="J5" s="5" t="inlineStr">
@@ -764,7 +764,7 @@
       <c r="H6" s="2" t="inlineStr"/>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>JCS</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr"/>
@@ -804,7 +804,7 @@
       <c r="H7" s="5" t="inlineStr"/>
       <c r="I7" s="5" t="inlineStr">
         <is>
-          <t>JCS</t>
+          <t>JM, MB, VB</t>
         </is>
       </c>
       <c r="J7" s="5" t="inlineStr">
@@ -848,7 +848,7 @@
       <c r="H8" s="2" t="inlineStr"/>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>JCS</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr"/>
@@ -888,7 +888,7 @@
       <c r="H9" s="5" t="inlineStr"/>
       <c r="I9" s="5" t="inlineStr">
         <is>
-          <t>JCS</t>
+          <t>JM, MB, VB</t>
         </is>
       </c>
       <c r="J9" s="5" t="inlineStr"/>
@@ -928,7 +928,7 @@
       <c r="H10" s="2" t="inlineStr"/>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>JCS</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr"/>
@@ -968,7 +968,7 @@
       <c r="H11" s="5" t="inlineStr"/>
       <c r="I11" s="5" t="inlineStr">
         <is>
-          <t>JCS</t>
+          <t>JM, MB, VB</t>
         </is>
       </c>
       <c r="J11" s="5" t="inlineStr"/>
@@ -1008,7 +1008,7 @@
       <c r="H12" s="2" t="inlineStr"/>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>JCS</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr"/>
@@ -1048,7 +1048,7 @@
       <c r="H13" s="5" t="inlineStr"/>
       <c r="I13" s="5" t="inlineStr">
         <is>
-          <t>JCS</t>
+          <t>JM, MB, VB</t>
         </is>
       </c>
       <c r="J13" s="5" t="inlineStr"/>
@@ -1092,7 +1092,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>JCS</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1136,7 +1136,7 @@
       <c r="H15" s="5" t="inlineStr"/>
       <c r="I15" s="5" t="inlineStr">
         <is>
-          <t>JCS</t>
+          <t>JM, MB, VB</t>
         </is>
       </c>
       <c r="J15" s="5" t="inlineStr"/>
@@ -1176,7 +1176,7 @@
       <c r="H16" s="2" t="inlineStr"/>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>JCS</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr"/>
@@ -1216,7 +1216,7 @@
       <c r="H17" s="5" t="inlineStr"/>
       <c r="I17" s="5" t="inlineStr">
         <is>
-          <t>JCS</t>
+          <t>JM, MB, VB</t>
         </is>
       </c>
       <c r="J17" s="5" t="inlineStr"/>
@@ -1256,7 +1256,7 @@
       <c r="H18" s="2" t="inlineStr"/>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>JCS</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr"/>
@@ -1300,7 +1300,7 @@
       </c>
       <c r="I19" s="5" t="inlineStr">
         <is>
-          <t>JCS</t>
+          <t>JM, MB, VB</t>
         </is>
       </c>
       <c r="J19" s="5" t="inlineStr">
@@ -1344,7 +1344,7 @@
       <c r="H20" s="2" t="inlineStr"/>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>JCS</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr"/>
@@ -1384,7 +1384,7 @@
       <c r="H21" s="5" t="inlineStr"/>
       <c r="I21" s="5" t="inlineStr">
         <is>
-          <t>JCS</t>
+          <t>JM, MB, VB</t>
         </is>
       </c>
       <c r="J21" s="5" t="inlineStr"/>
@@ -1424,7 +1424,7 @@
       <c r="H22" s="2" t="inlineStr"/>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>JCS</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr"/>
@@ -1464,7 +1464,7 @@
       <c r="H23" s="5" t="inlineStr"/>
       <c r="I23" s="5" t="inlineStr">
         <is>
-          <t>JCS</t>
+          <t>JM, MB, VB</t>
         </is>
       </c>
       <c r="J23" s="5" t="inlineStr"/>
@@ -1504,7 +1504,7 @@
       <c r="H24" s="2" t="inlineStr"/>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>JCS</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr"/>
@@ -1548,7 +1548,7 @@
       </c>
       <c r="I25" s="5" t="inlineStr">
         <is>
-          <t>JCS</t>
+          <t>JM, MB, VB</t>
         </is>
       </c>
       <c r="J25" s="5" t="inlineStr">
@@ -1592,7 +1592,7 @@
       <c r="H26" s="2" t="inlineStr"/>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>JCS</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr"/>
@@ -1632,7 +1632,7 @@
       <c r="H27" s="5" t="inlineStr"/>
       <c r="I27" s="5" t="inlineStr">
         <is>
-          <t>JCS</t>
+          <t>JM, MB, VB</t>
         </is>
       </c>
       <c r="J27" s="5" t="inlineStr"/>
@@ -1672,7 +1672,7 @@
       <c r="H28" s="2" t="inlineStr"/>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>JCS</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr"/>
@@ -1716,7 +1716,7 @@
       </c>
       <c r="I29" s="5" t="inlineStr">
         <is>
-          <t>JCS</t>
+          <t>JM, MB, VB</t>
         </is>
       </c>
       <c r="J29" s="5" t="inlineStr">
@@ -1760,7 +1760,7 @@
       <c r="H30" s="2" t="inlineStr"/>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>JCS</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr"/>
@@ -1800,7 +1800,7 @@
       <c r="H31" s="5" t="inlineStr"/>
       <c r="I31" s="5" t="inlineStr">
         <is>
-          <t>JCS</t>
+          <t>JM, MB, VB</t>
         </is>
       </c>
       <c r="J31" s="5" t="inlineStr"/>
@@ -1844,7 +1844,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>JCS</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -1888,7 +1888,7 @@
       <c r="H33" s="5" t="inlineStr"/>
       <c r="I33" s="5" t="inlineStr">
         <is>
-          <t>JCS</t>
+          <t>JM, MB, VB</t>
         </is>
       </c>
       <c r="J33" s="5" t="inlineStr"/>
@@ -1928,7 +1928,7 @@
       <c r="H34" s="9" t="inlineStr"/>
       <c r="I34" s="9" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>JCS</t>
         </is>
       </c>
       <c r="J34" s="9" t="inlineStr">
@@ -1972,7 +1972,7 @@
       <c r="H35" s="9" t="inlineStr"/>
       <c r="I35" s="9" t="inlineStr">
         <is>
-          <t>JCS</t>
+          <t>JM, MB, VB</t>
         </is>
       </c>
       <c r="J35" s="9" t="inlineStr">
@@ -2020,7 +2020,7 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>JCS</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -2064,7 +2064,7 @@
       <c r="H37" s="5" t="inlineStr"/>
       <c r="I37" s="5" t="inlineStr">
         <is>
-          <t>JCS</t>
+          <t>JM, MB, VB</t>
         </is>
       </c>
       <c r="J37" s="5" t="inlineStr"/>
@@ -2108,7 +2108,7 @@
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>JCS</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -2152,7 +2152,7 @@
       <c r="H39" s="5" t="inlineStr"/>
       <c r="I39" s="5" t="inlineStr">
         <is>
-          <t>JCS</t>
+          <t>JM, MB, VB</t>
         </is>
       </c>
       <c r="J39" s="5" t="inlineStr"/>
@@ -2232,7 +2232,7 @@
       <c r="H41" s="5" t="inlineStr"/>
       <c r="I41" s="5" t="inlineStr">
         <is>
-          <t>JCS</t>
+          <t>NV, RM, SM</t>
         </is>
       </c>
       <c r="J41" s="5" t="inlineStr"/>
@@ -2316,7 +2316,7 @@
       </c>
       <c r="I43" s="5" t="inlineStr">
         <is>
-          <t>JCS</t>
+          <t>NV, RM, SM</t>
         </is>
       </c>
       <c r="J43" s="5" t="inlineStr">
@@ -2400,7 +2400,7 @@
       <c r="H45" s="12" t="inlineStr"/>
       <c r="I45" s="12" t="inlineStr">
         <is>
-          <t>JCS</t>
+          <t>NV, RM, SM</t>
         </is>
       </c>
       <c r="J45" s="12" t="inlineStr">
@@ -2484,7 +2484,7 @@
       <c r="H47" s="5" t="inlineStr"/>
       <c r="I47" s="5" t="inlineStr">
         <is>
-          <t>JCS</t>
+          <t>NV, RM, SM</t>
         </is>
       </c>
       <c r="J47" s="5" t="inlineStr"/>
@@ -2564,7 +2564,7 @@
       <c r="H49" s="5" t="inlineStr"/>
       <c r="I49" s="5" t="inlineStr">
         <is>
-          <t>JCS</t>
+          <t>NV, RM, SM</t>
         </is>
       </c>
       <c r="J49" s="5" t="inlineStr"/>
@@ -2644,7 +2644,7 @@
       <c r="H51" s="5" t="inlineStr"/>
       <c r="I51" s="5" t="inlineStr">
         <is>
-          <t>JCS</t>
+          <t>NV, RM, SM</t>
         </is>
       </c>
       <c r="J51" s="5" t="inlineStr"/>
@@ -2732,7 +2732,7 @@
       <c r="H53" s="12" t="inlineStr"/>
       <c r="I53" s="12" t="inlineStr">
         <is>
-          <t>JCS</t>
+          <t>NV, RM, SM</t>
         </is>
       </c>
       <c r="J53" s="12" t="inlineStr">
@@ -2816,7 +2816,7 @@
       <c r="H55" s="5" t="inlineStr"/>
       <c r="I55" s="5" t="inlineStr">
         <is>
-          <t>JCS</t>
+          <t>NV, RM, SM</t>
         </is>
       </c>
       <c r="J55" s="5" t="inlineStr"/>
@@ -2900,7 +2900,7 @@
       </c>
       <c r="I57" s="5" t="inlineStr">
         <is>
-          <t>JCS</t>
+          <t>NV, RM, SM</t>
         </is>
       </c>
       <c r="J57" s="5" t="inlineStr">
@@ -2984,7 +2984,7 @@
       <c r="H59" s="5" t="inlineStr"/>
       <c r="I59" s="5" t="inlineStr">
         <is>
-          <t>JCS</t>
+          <t>NV, RM, SM</t>
         </is>
       </c>
       <c r="J59" s="5" t="inlineStr"/>
@@ -3064,7 +3064,7 @@
       <c r="H61" s="5" t="inlineStr"/>
       <c r="I61" s="5" t="inlineStr">
         <is>
-          <t>JCS</t>
+          <t>NV, RM, SM</t>
         </is>
       </c>
       <c r="J61" s="5" t="inlineStr"/>
@@ -3148,7 +3148,7 @@
       </c>
       <c r="I63" s="5" t="inlineStr">
         <is>
-          <t>JCS</t>
+          <t>NV, RM, SM</t>
         </is>
       </c>
       <c r="J63" s="5" t="inlineStr">
@@ -3232,7 +3232,7 @@
       <c r="H65" s="5" t="inlineStr"/>
       <c r="I65" s="5" t="inlineStr">
         <is>
-          <t>JCS</t>
+          <t>NV, RM, SM</t>
         </is>
       </c>
       <c r="J65" s="5" t="inlineStr"/>
@@ -3316,7 +3316,7 @@
       </c>
       <c r="I67" s="5" t="inlineStr">
         <is>
-          <t>JCS</t>
+          <t>NV, RM, SM</t>
         </is>
       </c>
       <c r="J67" s="5" t="inlineStr">
@@ -3400,7 +3400,7 @@
       <c r="H69" s="5" t="inlineStr"/>
       <c r="I69" s="5" t="inlineStr">
         <is>
-          <t>JCS</t>
+          <t>NV, RM, SM</t>
         </is>
       </c>
       <c r="J69" s="5" t="inlineStr"/>
@@ -3488,7 +3488,7 @@
       <c r="H71" s="5" t="inlineStr"/>
       <c r="I71" s="5" t="inlineStr">
         <is>
-          <t>JCS</t>
+          <t>NV, RM, SM</t>
         </is>
       </c>
       <c r="J71" s="5" t="inlineStr"/>
@@ -3572,7 +3572,7 @@
       <c r="H73" s="9" t="inlineStr"/>
       <c r="I73" s="9" t="inlineStr">
         <is>
-          <t>JCS</t>
+          <t>NV, RM, SM</t>
         </is>
       </c>
       <c r="J73" s="9" t="inlineStr">
@@ -3664,7 +3664,7 @@
       <c r="H75" s="5" t="inlineStr"/>
       <c r="I75" s="5" t="inlineStr">
         <is>
-          <t>JCS</t>
+          <t>NV, RM, SM</t>
         </is>
       </c>
       <c r="J75" s="5" t="inlineStr"/>
@@ -3752,7 +3752,7 @@
       <c r="H77" s="5" t="inlineStr"/>
       <c r="I77" s="5" t="inlineStr">
         <is>
-          <t>JCS</t>
+          <t>NV, RM, SM</t>
         </is>
       </c>
       <c r="J77" s="5" t="inlineStr"/>
@@ -3792,7 +3792,7 @@
       <c r="H78" s="2" t="inlineStr"/>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>IG</t>
         </is>
       </c>
       <c r="J78" s="2" t="inlineStr"/>
@@ -3832,7 +3832,7 @@
       <c r="H79" s="5" t="inlineStr"/>
       <c r="I79" s="5" t="inlineStr">
         <is>
-          <t>JCS</t>
+          <t>MB, GM, DH</t>
         </is>
       </c>
       <c r="J79" s="5" t="inlineStr"/>
@@ -3872,7 +3872,7 @@
       <c r="H80" s="2" t="inlineStr"/>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>IG</t>
         </is>
       </c>
       <c r="J80" s="2" t="inlineStr"/>
@@ -3916,7 +3916,7 @@
       </c>
       <c r="I81" s="5" t="inlineStr">
         <is>
-          <t>JCS</t>
+          <t>MB, GM, DH</t>
         </is>
       </c>
       <c r="J81" s="5" t="inlineStr">
@@ -3960,7 +3960,7 @@
       <c r="H82" s="2" t="inlineStr"/>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>IG</t>
         </is>
       </c>
       <c r="J82" s="2" t="inlineStr"/>
@@ -4000,7 +4000,7 @@
       <c r="H83" s="12" t="inlineStr"/>
       <c r="I83" s="12" t="inlineStr">
         <is>
-          <t>JCS</t>
+          <t>MB, GM, DH</t>
         </is>
       </c>
       <c r="J83" s="12" t="inlineStr">
@@ -4044,7 +4044,7 @@
       <c r="H84" s="2" t="inlineStr"/>
       <c r="I84" s="2" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>IG</t>
         </is>
       </c>
       <c r="J84" s="2" t="inlineStr"/>
@@ -4084,7 +4084,7 @@
       <c r="H85" s="5" t="inlineStr"/>
       <c r="I85" s="5" t="inlineStr">
         <is>
-          <t>JCS</t>
+          <t>MB, GM, DH</t>
         </is>
       </c>
       <c r="J85" s="5" t="inlineStr"/>
@@ -4124,7 +4124,7 @@
       <c r="H86" s="2" t="inlineStr"/>
       <c r="I86" s="2" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>IG</t>
         </is>
       </c>
       <c r="J86" s="2" t="inlineStr"/>
@@ -4164,7 +4164,7 @@
       <c r="H87" s="5" t="inlineStr"/>
       <c r="I87" s="5" t="inlineStr">
         <is>
-          <t>JCS</t>
+          <t>MB, GM, DH</t>
         </is>
       </c>
       <c r="J87" s="5" t="inlineStr"/>
@@ -4204,7 +4204,7 @@
       <c r="H88" s="2" t="inlineStr"/>
       <c r="I88" s="2" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>IG</t>
         </is>
       </c>
       <c r="J88" s="2" t="inlineStr"/>
@@ -4244,7 +4244,7 @@
       <c r="H89" s="5" t="inlineStr"/>
       <c r="I89" s="5" t="inlineStr">
         <is>
-          <t>JCS</t>
+          <t>MB, GM, DH</t>
         </is>
       </c>
       <c r="J89" s="5" t="inlineStr"/>
@@ -4288,7 +4288,7 @@
       </c>
       <c r="I90" s="2" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>IG</t>
         </is>
       </c>
       <c r="J90" s="2" t="inlineStr">
@@ -4332,7 +4332,7 @@
       <c r="H91" s="12" t="inlineStr"/>
       <c r="I91" s="12" t="inlineStr">
         <is>
-          <t>JCS</t>
+          <t>MB, GM, DH</t>
         </is>
       </c>
       <c r="J91" s="12" t="inlineStr">
@@ -4376,7 +4376,7 @@
       <c r="H92" s="2" t="inlineStr"/>
       <c r="I92" s="2" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>IG</t>
         </is>
       </c>
       <c r="J92" s="2" t="inlineStr"/>
@@ -4416,7 +4416,7 @@
       <c r="H93" s="5" t="inlineStr"/>
       <c r="I93" s="5" t="inlineStr">
         <is>
-          <t>JCS</t>
+          <t>MB, GM, DH</t>
         </is>
       </c>
       <c r="J93" s="5" t="inlineStr"/>
@@ -4456,7 +4456,7 @@
       <c r="H94" s="2" t="inlineStr"/>
       <c r="I94" s="2" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>IG</t>
         </is>
       </c>
       <c r="J94" s="2" t="inlineStr"/>
@@ -4500,7 +4500,7 @@
       </c>
       <c r="I95" s="5" t="inlineStr">
         <is>
-          <t>JCS</t>
+          <t>MB, GM, DH</t>
         </is>
       </c>
       <c r="J95" s="5" t="inlineStr">
@@ -4544,7 +4544,7 @@
       <c r="H96" s="2" t="inlineStr"/>
       <c r="I96" s="2" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>IG</t>
         </is>
       </c>
       <c r="J96" s="2" t="inlineStr"/>
@@ -4584,7 +4584,7 @@
       <c r="H97" s="5" t="inlineStr"/>
       <c r="I97" s="5" t="inlineStr">
         <is>
-          <t>JCS</t>
+          <t>MB, GM, DH</t>
         </is>
       </c>
       <c r="J97" s="5" t="inlineStr"/>
@@ -4624,7 +4624,7 @@
       <c r="H98" s="2" t="inlineStr"/>
       <c r="I98" s="2" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>IG</t>
         </is>
       </c>
       <c r="J98" s="2" t="inlineStr"/>
@@ -4664,7 +4664,7 @@
       <c r="H99" s="5" t="inlineStr"/>
       <c r="I99" s="5" t="inlineStr">
         <is>
-          <t>JCS</t>
+          <t>MB, GM, DH</t>
         </is>
       </c>
       <c r="J99" s="5" t="inlineStr"/>
@@ -4704,7 +4704,7 @@
       <c r="H100" s="2" t="inlineStr"/>
       <c r="I100" s="2" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>IG</t>
         </is>
       </c>
       <c r="J100" s="2" t="inlineStr"/>
@@ -4748,7 +4748,7 @@
       </c>
       <c r="I101" s="5" t="inlineStr">
         <is>
-          <t>JCS</t>
+          <t>MB, GM, DH</t>
         </is>
       </c>
       <c r="J101" s="5" t="inlineStr">
@@ -4792,7 +4792,7 @@
       <c r="H102" s="2" t="inlineStr"/>
       <c r="I102" s="2" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>IG</t>
         </is>
       </c>
       <c r="J102" s="2" t="inlineStr"/>
@@ -4832,7 +4832,7 @@
       <c r="H103" s="5" t="inlineStr"/>
       <c r="I103" s="5" t="inlineStr">
         <is>
-          <t>JCS</t>
+          <t>MB, GM, DH</t>
         </is>
       </c>
       <c r="J103" s="5" t="inlineStr"/>
@@ -4872,7 +4872,7 @@
       <c r="H104" s="2" t="inlineStr"/>
       <c r="I104" s="2" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>IG</t>
         </is>
       </c>
       <c r="J104" s="2" t="inlineStr"/>
@@ -4916,7 +4916,7 @@
       </c>
       <c r="I105" s="5" t="inlineStr">
         <is>
-          <t>JCS</t>
+          <t>MB, GM, DH</t>
         </is>
       </c>
       <c r="J105" s="5" t="inlineStr">
@@ -4960,7 +4960,7 @@
       <c r="H106" s="2" t="inlineStr"/>
       <c r="I106" s="2" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>IG</t>
         </is>
       </c>
       <c r="J106" s="2" t="inlineStr"/>
@@ -5000,7 +5000,7 @@
       <c r="H107" s="5" t="inlineStr"/>
       <c r="I107" s="5" t="inlineStr">
         <is>
-          <t>JCS</t>
+          <t>MB, GM, DH</t>
         </is>
       </c>
       <c r="J107" s="5" t="inlineStr"/>
@@ -5044,7 +5044,7 @@
       </c>
       <c r="I108" s="2" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>IG</t>
         </is>
       </c>
       <c r="J108" s="2" t="inlineStr">
@@ -5088,7 +5088,7 @@
       <c r="H109" s="5" t="inlineStr"/>
       <c r="I109" s="5" t="inlineStr">
         <is>
-          <t>JCS</t>
+          <t>MB, GM, DH</t>
         </is>
       </c>
       <c r="J109" s="5" t="inlineStr"/>
@@ -5128,7 +5128,7 @@
       <c r="H110" s="9" t="inlineStr"/>
       <c r="I110" s="9" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>IG</t>
         </is>
       </c>
       <c r="J110" s="9" t="inlineStr">
@@ -5172,7 +5172,7 @@
       <c r="H111" s="9" t="inlineStr"/>
       <c r="I111" s="9" t="inlineStr">
         <is>
-          <t>JCS</t>
+          <t>MB, GM, DH</t>
         </is>
       </c>
       <c r="J111" s="9" t="inlineStr">
@@ -5220,7 +5220,7 @@
       </c>
       <c r="I112" s="2" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>IG</t>
         </is>
       </c>
       <c r="J112" s="2" t="inlineStr">
@@ -5264,7 +5264,7 @@
       <c r="H113" s="5" t="inlineStr"/>
       <c r="I113" s="5" t="inlineStr">
         <is>
-          <t>JCS</t>
+          <t>MB, GM, DH</t>
         </is>
       </c>
       <c r="J113" s="5" t="inlineStr"/>
@@ -5308,7 +5308,7 @@
       </c>
       <c r="I114" s="2" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>IG</t>
         </is>
       </c>
       <c r="J114" s="2" t="inlineStr">
@@ -5352,7 +5352,7 @@
       <c r="H115" s="5" t="inlineStr"/>
       <c r="I115" s="5" t="inlineStr">
         <is>
-          <t>JCS</t>
+          <t>MB, GM, DH</t>
         </is>
       </c>
       <c r="J115" s="5" t="inlineStr"/>
@@ -5392,7 +5392,7 @@
       <c r="H116" s="2" t="inlineStr"/>
       <c r="I116" s="2" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>CC</t>
         </is>
       </c>
       <c r="J116" s="2" t="inlineStr"/>
@@ -5432,7 +5432,7 @@
       <c r="H117" s="5" t="inlineStr"/>
       <c r="I117" s="5" t="inlineStr">
         <is>
-          <t>JCS</t>
+          <t>DH, GM, VB</t>
         </is>
       </c>
       <c r="J117" s="5" t="inlineStr"/>
@@ -5472,7 +5472,7 @@
       <c r="H118" s="2" t="inlineStr"/>
       <c r="I118" s="2" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>CC</t>
         </is>
       </c>
       <c r="J118" s="2" t="inlineStr"/>
@@ -5516,7 +5516,7 @@
       </c>
       <c r="I119" s="5" t="inlineStr">
         <is>
-          <t>JCS</t>
+          <t>DH, GM, VB</t>
         </is>
       </c>
       <c r="J119" s="5" t="inlineStr">
@@ -5560,7 +5560,7 @@
       <c r="H120" s="2" t="inlineStr"/>
       <c r="I120" s="2" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>CC</t>
         </is>
       </c>
       <c r="J120" s="2" t="inlineStr"/>
@@ -5600,7 +5600,7 @@
       <c r="H121" s="12" t="inlineStr"/>
       <c r="I121" s="12" t="inlineStr">
         <is>
-          <t>JCS</t>
+          <t>DH, GM, VB</t>
         </is>
       </c>
       <c r="J121" s="12" t="inlineStr">
@@ -5644,7 +5644,7 @@
       <c r="H122" s="2" t="inlineStr"/>
       <c r="I122" s="2" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>CC</t>
         </is>
       </c>
       <c r="J122" s="2" t="inlineStr"/>
@@ -5684,7 +5684,7 @@
       <c r="H123" s="5" t="inlineStr"/>
       <c r="I123" s="5" t="inlineStr">
         <is>
-          <t>JCS</t>
+          <t>DH, GM, VB</t>
         </is>
       </c>
       <c r="J123" s="5" t="inlineStr"/>
@@ -5724,7 +5724,7 @@
       <c r="H124" s="2" t="inlineStr"/>
       <c r="I124" s="2" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>CC</t>
         </is>
       </c>
       <c r="J124" s="2" t="inlineStr"/>
@@ -5764,7 +5764,7 @@
       <c r="H125" s="5" t="inlineStr"/>
       <c r="I125" s="5" t="inlineStr">
         <is>
-          <t>JCS</t>
+          <t>DH, GM, VB</t>
         </is>
       </c>
       <c r="J125" s="5" t="inlineStr"/>
@@ -5804,7 +5804,7 @@
       <c r="H126" s="2" t="inlineStr"/>
       <c r="I126" s="2" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>CC</t>
         </is>
       </c>
       <c r="J126" s="2" t="inlineStr"/>
@@ -5844,7 +5844,7 @@
       <c r="H127" s="5" t="inlineStr"/>
       <c r="I127" s="5" t="inlineStr">
         <is>
-          <t>JCS</t>
+          <t>DH, GM, VB</t>
         </is>
       </c>
       <c r="J127" s="5" t="inlineStr"/>
@@ -5888,7 +5888,7 @@
       </c>
       <c r="I128" s="2" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>CC</t>
         </is>
       </c>
       <c r="J128" s="2" t="inlineStr">
@@ -5932,7 +5932,7 @@
       <c r="H129" s="12" t="inlineStr"/>
       <c r="I129" s="12" t="inlineStr">
         <is>
-          <t>JCS</t>
+          <t>DH, GM, VB</t>
         </is>
       </c>
       <c r="J129" s="12" t="inlineStr">
@@ -5976,7 +5976,7 @@
       <c r="H130" s="2" t="inlineStr"/>
       <c r="I130" s="2" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>CC</t>
         </is>
       </c>
       <c r="J130" s="2" t="inlineStr"/>
@@ -6016,7 +6016,7 @@
       <c r="H131" s="5" t="inlineStr"/>
       <c r="I131" s="5" t="inlineStr">
         <is>
-          <t>JCS</t>
+          <t>DH, GM, VB</t>
         </is>
       </c>
       <c r="J131" s="5" t="inlineStr"/>
@@ -6056,7 +6056,7 @@
       <c r="H132" s="2" t="inlineStr"/>
       <c r="I132" s="2" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>CC</t>
         </is>
       </c>
       <c r="J132" s="2" t="inlineStr"/>
@@ -6100,7 +6100,7 @@
       </c>
       <c r="I133" s="5" t="inlineStr">
         <is>
-          <t>JCS</t>
+          <t>DH, GM, VB</t>
         </is>
       </c>
       <c r="J133" s="5" t="inlineStr">
@@ -6144,7 +6144,7 @@
       <c r="H134" s="2" t="inlineStr"/>
       <c r="I134" s="2" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>CC</t>
         </is>
       </c>
       <c r="J134" s="2" t="inlineStr"/>
@@ -6184,7 +6184,7 @@
       <c r="H135" s="5" t="inlineStr"/>
       <c r="I135" s="5" t="inlineStr">
         <is>
-          <t>JCS</t>
+          <t>DH, GM, VB</t>
         </is>
       </c>
       <c r="J135" s="5" t="inlineStr"/>
@@ -6224,7 +6224,7 @@
       <c r="H136" s="2" t="inlineStr"/>
       <c r="I136" s="2" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>CC</t>
         </is>
       </c>
       <c r="J136" s="2" t="inlineStr"/>
@@ -6264,7 +6264,7 @@
       <c r="H137" s="5" t="inlineStr"/>
       <c r="I137" s="5" t="inlineStr">
         <is>
-          <t>JCS</t>
+          <t>DH, GM, VB</t>
         </is>
       </c>
       <c r="J137" s="5" t="inlineStr"/>
@@ -6304,7 +6304,7 @@
       <c r="H138" s="2" t="inlineStr"/>
       <c r="I138" s="2" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>CC</t>
         </is>
       </c>
       <c r="J138" s="2" t="inlineStr"/>
@@ -6348,7 +6348,7 @@
       </c>
       <c r="I139" s="5" t="inlineStr">
         <is>
-          <t>JCS</t>
+          <t>DH, GM, VB</t>
         </is>
       </c>
       <c r="J139" s="5" t="inlineStr">
@@ -6392,7 +6392,7 @@
       <c r="H140" s="2" t="inlineStr"/>
       <c r="I140" s="2" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>CC</t>
         </is>
       </c>
       <c r="J140" s="2" t="inlineStr"/>
@@ -6432,7 +6432,7 @@
       <c r="H141" s="5" t="inlineStr"/>
       <c r="I141" s="5" t="inlineStr">
         <is>
-          <t>JCS</t>
+          <t>DH, GM, VB</t>
         </is>
       </c>
       <c r="J141" s="5" t="inlineStr"/>
@@ -6472,7 +6472,7 @@
       <c r="H142" s="2" t="inlineStr"/>
       <c r="I142" s="2" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>CC</t>
         </is>
       </c>
       <c r="J142" s="2" t="inlineStr"/>
@@ -6516,7 +6516,7 @@
       </c>
       <c r="I143" s="5" t="inlineStr">
         <is>
-          <t>JCS</t>
+          <t>DH, GM, VB</t>
         </is>
       </c>
       <c r="J143" s="5" t="inlineStr">
@@ -6560,7 +6560,7 @@
       <c r="H144" s="2" t="inlineStr"/>
       <c r="I144" s="2" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>CC</t>
         </is>
       </c>
       <c r="J144" s="2" t="inlineStr"/>
@@ -6600,7 +6600,7 @@
       <c r="H145" s="5" t="inlineStr"/>
       <c r="I145" s="5" t="inlineStr">
         <is>
-          <t>JCS</t>
+          <t>DH, GM, VB</t>
         </is>
       </c>
       <c r="J145" s="5" t="inlineStr"/>
@@ -6644,7 +6644,7 @@
       </c>
       <c r="I146" s="2" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>CC</t>
         </is>
       </c>
       <c r="J146" s="2" t="inlineStr">
@@ -6688,7 +6688,7 @@
       <c r="H147" s="5" t="inlineStr"/>
       <c r="I147" s="5" t="inlineStr">
         <is>
-          <t>JCS</t>
+          <t>DH, GM, VB</t>
         </is>
       </c>
       <c r="J147" s="5" t="inlineStr"/>
@@ -6728,7 +6728,7 @@
       <c r="H148" s="9" t="inlineStr"/>
       <c r="I148" s="9" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>CC</t>
         </is>
       </c>
       <c r="J148" s="9" t="inlineStr">
@@ -6772,7 +6772,7 @@
       <c r="H149" s="9" t="inlineStr"/>
       <c r="I149" s="9" t="inlineStr">
         <is>
-          <t>JCS</t>
+          <t>DH, GM, VB</t>
         </is>
       </c>
       <c r="J149" s="9" t="inlineStr">
@@ -6820,7 +6820,7 @@
       </c>
       <c r="I150" s="2" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>CC</t>
         </is>
       </c>
       <c r="J150" s="2" t="inlineStr">
@@ -6864,7 +6864,7 @@
       <c r="H151" s="5" t="inlineStr"/>
       <c r="I151" s="5" t="inlineStr">
         <is>
-          <t>JCS</t>
+          <t>DH, GM, VB</t>
         </is>
       </c>
       <c r="J151" s="5" t="inlineStr"/>
@@ -6908,7 +6908,7 @@
       </c>
       <c r="I152" s="2" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>CC</t>
         </is>
       </c>
       <c r="J152" s="2" t="inlineStr">
@@ -6952,7 +6952,7 @@
       <c r="H153" s="5" t="inlineStr"/>
       <c r="I153" s="5" t="inlineStr">
         <is>
-          <t>JCS</t>
+          <t>DH, GM, VB</t>
         </is>
       </c>
       <c r="J153" s="5" t="inlineStr"/>

--- a/data/enobnu/calendario.xlsx
+++ b/data/enobnu/calendario.xlsx
@@ -715,7 +715,7 @@
       </c>
       <c r="H5" s="8" t="inlineStr">
         <is>
-          <t>Control</t>
+          <t>Taller</t>
         </is>
       </c>
       <c r="I5" s="5" t="inlineStr">
@@ -1295,7 +1295,7 @@
       </c>
       <c r="H19" s="8" t="inlineStr">
         <is>
-          <t>Control</t>
+          <t>Taller</t>
         </is>
       </c>
       <c r="I19" s="5" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="H29" s="8" t="inlineStr">
         <is>
-          <t>Control</t>
+          <t>Taller</t>
         </is>
       </c>
       <c r="I29" s="5" t="inlineStr">
@@ -2311,7 +2311,7 @@
       </c>
       <c r="H43" s="8" t="inlineStr">
         <is>
-          <t>Control</t>
+          <t>Taller</t>
         </is>
       </c>
       <c r="I43" s="5" t="inlineStr">
@@ -2895,7 +2895,7 @@
       </c>
       <c r="H57" s="8" t="inlineStr">
         <is>
-          <t>Control</t>
+          <t>Taller</t>
         </is>
       </c>
       <c r="I57" s="5" t="inlineStr">
@@ -3311,7 +3311,7 @@
       </c>
       <c r="H67" s="8" t="inlineStr">
         <is>
-          <t>Control</t>
+          <t>Taller</t>
         </is>
       </c>
       <c r="I67" s="5" t="inlineStr">
@@ -3911,7 +3911,7 @@
       </c>
       <c r="H81" s="8" t="inlineStr">
         <is>
-          <t>Control</t>
+          <t>Taller</t>
         </is>
       </c>
       <c r="I81" s="5" t="inlineStr">
@@ -4495,7 +4495,7 @@
       </c>
       <c r="H95" s="8" t="inlineStr">
         <is>
-          <t>Control</t>
+          <t>Taller</t>
         </is>
       </c>
       <c r="I95" s="5" t="inlineStr">
@@ -4911,7 +4911,7 @@
       </c>
       <c r="H105" s="8" t="inlineStr">
         <is>
-          <t>Control</t>
+          <t>Taller</t>
         </is>
       </c>
       <c r="I105" s="5" t="inlineStr">
@@ -5511,7 +5511,7 @@
       </c>
       <c r="H119" s="8" t="inlineStr">
         <is>
-          <t>Control</t>
+          <t>Taller</t>
         </is>
       </c>
       <c r="I119" s="5" t="inlineStr">
@@ -6095,7 +6095,7 @@
       </c>
       <c r="H133" s="8" t="inlineStr">
         <is>
-          <t>Control</t>
+          <t>Taller</t>
         </is>
       </c>
       <c r="I133" s="5" t="inlineStr">
@@ -6511,7 +6511,7 @@
       </c>
       <c r="H143" s="8" t="inlineStr">
         <is>
-          <t>Control</t>
+          <t>Taller</t>
         </is>
       </c>
       <c r="I143" s="5" t="inlineStr">

--- a/data/enobnu/calendario.xlsx
+++ b/data/enobnu/calendario.xlsx
@@ -1969,7 +1969,11 @@
           <t>Trabajo Autónomo</t>
         </is>
       </c>
-      <c r="H35" s="9" t="inlineStr"/>
+      <c r="H35" s="8" t="inlineStr">
+        <is>
+          <t>Portafolio</t>
+        </is>
+      </c>
       <c r="I35" s="9" t="inlineStr">
         <is>
           <t>JM, MB, VB</t>
@@ -3569,7 +3573,11 @@
           <t>Trabajo Autónomo</t>
         </is>
       </c>
-      <c r="H73" s="9" t="inlineStr"/>
+      <c r="H73" s="8" t="inlineStr">
+        <is>
+          <t>Portafolio</t>
+        </is>
+      </c>
       <c r="I73" s="9" t="inlineStr">
         <is>
           <t>NV, RM, SM</t>
@@ -5169,7 +5177,11 @@
           <t>Trabajo Autónomo</t>
         </is>
       </c>
-      <c r="H111" s="9" t="inlineStr"/>
+      <c r="H111" s="8" t="inlineStr">
+        <is>
+          <t>Portafolio</t>
+        </is>
+      </c>
       <c r="I111" s="9" t="inlineStr">
         <is>
           <t>MB, GM, DH</t>
@@ -6769,7 +6781,11 @@
           <t>Trabajo Autónomo</t>
         </is>
       </c>
-      <c r="H149" s="9" t="inlineStr"/>
+      <c r="H149" s="8" t="inlineStr">
+        <is>
+          <t>Portafolio</t>
+        </is>
+      </c>
       <c r="I149" s="9" t="inlineStr">
         <is>
           <t>DH, GM, VB</t>

--- a/data/enobnu/calendario.xlsx
+++ b/data/enobnu/calendario.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Calendario" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Calendario" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Calendario'!$A$1:$J$153</definedName>
@@ -1210,7 +1210,7 @@
       </c>
       <c r="G17" s="5" t="inlineStr">
         <is>
-          <t>Revisión Certamen 1</t>
+          <t>Modelos y Derivadas 4</t>
         </is>
       </c>
       <c r="H17" s="5" t="inlineStr"/>
@@ -1290,7 +1290,7 @@
       </c>
       <c r="G19" s="5" t="inlineStr">
         <is>
-          <t>Modelos y Derivadas 4</t>
+          <t>Revisión Certamen 1</t>
         </is>
       </c>
       <c r="H19" s="8" t="inlineStr">
@@ -2814,7 +2814,7 @@
       </c>
       <c r="G55" s="5" t="inlineStr">
         <is>
-          <t>Revisión Certamen 1</t>
+          <t>Modelos y Derivadas 4</t>
         </is>
       </c>
       <c r="H55" s="5" t="inlineStr"/>
@@ -2894,7 +2894,7 @@
       </c>
       <c r="G57" s="5" t="inlineStr">
         <is>
-          <t>Modelos y Derivadas 4</t>
+          <t>Revisión Certamen 1</t>
         </is>
       </c>
       <c r="H57" s="8" t="inlineStr">
@@ -4418,7 +4418,7 @@
       </c>
       <c r="G93" s="5" t="inlineStr">
         <is>
-          <t>Revisión Certamen 1</t>
+          <t>Modelos y Derivadas 4</t>
         </is>
       </c>
       <c r="H93" s="5" t="inlineStr"/>
@@ -4498,7 +4498,7 @@
       </c>
       <c r="G95" s="5" t="inlineStr">
         <is>
-          <t>Modelos y Derivadas 4</t>
+          <t>Revisión Certamen 1</t>
         </is>
       </c>
       <c r="H95" s="8" t="inlineStr">
@@ -6022,7 +6022,7 @@
       </c>
       <c r="G131" s="5" t="inlineStr">
         <is>
-          <t>Revisión Certamen 1</t>
+          <t>Modelos y Derivadas 4</t>
         </is>
       </c>
       <c r="H131" s="5" t="inlineStr"/>
@@ -6102,7 +6102,7 @@
       </c>
       <c r="G133" s="5" t="inlineStr">
         <is>
-          <t>Modelos y Derivadas 4</t>
+          <t>Revisión Certamen 1</t>
         </is>
       </c>
       <c r="H133" s="8" t="inlineStr">
